--- a/VIRTUSSOLUTIONS_LLC_Audited_General_Ledger.xlsx
+++ b/VIRTUSSOLUTIONS_LLC_Audited_General_Ledger.xlsx
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -818,14 +818,14 @@
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>VIRTUSSOLUTIONS LLC - General Ledger Audit &amp; Compliance Summary</t>
+          <t>General Ledger Audit &amp; Compliance Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="42" t="inlineStr">
         <is>
-          <t>Period: July 2026 | Accounting Basis: Accrual Basis</t>
+          <t>Total Transactions Audited: 335 | Issues / Updates: 33</t>
         </is>
       </c>
     </row>
@@ -854,13 +854,13 @@
     </row>
     <row r="5">
       <c r="A5" s="46" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C5" s="47" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="46" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G5" s="48" t="n">
         <v>2</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="52" t="inlineStr">
         <is>
-          <t>Updated Name to 'Amex CC'</t>
+          <t>Set Vendor Name to 'Amex CC'</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="J9" s="52" t="inlineStr">
         <is>
-          <t>Updated Name to 'BOA CC'</t>
+          <t>Set Vendor Name to 'BOA CC'</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E10" s="52" t="inlineStr">
         <is>
-          <t>BKOFAMERICA MOBILE 07/29 37780</t>
+          <t>BKOFAMERICA MOBILE 07/29 3778024504</t>
         </is>
       </c>
       <c r="F10" s="51" t="inlineStr">
@@ -1065,35 +1065,35 @@
     </row>
     <row r="11">
       <c r="A11" s="50" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B11" s="50" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>07/31/2026</t>
         </is>
       </c>
       <c r="C11" s="51" t="inlineStr">
         <is>
-          <t>Amex CC</t>
+          <t>Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>Banner Pest Services</t>
+          <t>Sage Solutions</t>
         </is>
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
-          <t>PY *BANNER PEST SERVSAN JOSE            CA</t>
+          <t>Venkata Vinay Kumar 07/01/2026 -07/31/2026 (88*$77)</t>
         </is>
       </c>
       <c r="G11" s="53" t="n">
-        <v>150</v>
+        <v>6776</v>
       </c>
       <c r="H11" s="56" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="I11" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Office expenses:Office supplies)</t>
+          <t>Mismatched Category (Found: Accounts Payable (A/P))</t>
         </is>
       </c>
       <c r="J11" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Repairs &amp; maintenance'</t>
+          <t>Reclassify to historical category: 'Accounts Receivable (A/R)'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="50" t="n">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="B12" s="50" t="inlineStr">
         <is>
-          <t>07/24/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C12" s="51" t="inlineStr">
@@ -1127,45 +1127,45 @@
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>Credit Card Payment</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E12" s="52" t="inlineStr">
         <is>
-          <t>Amex CC</t>
+          <t>AMK BLACKROCKWILMINGTON          DE</t>
         </is>
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
-          <t>AMERICAN EXPRESS DES:ACH PMT ID:W4206 INDN:SNEHA DATLA CO ID:1133133497 CCD</t>
+          <t>AplPay AMK BLACKROCKWILMINGTON          DE</t>
         </is>
       </c>
       <c r="G12" s="53" t="n">
-        <v>-4823.19</v>
-      </c>
-      <c r="H12" s="54" t="inlineStr">
-        <is>
-          <t>CC VENDOR UPDATED</t>
+        <v>3.59</v>
+      </c>
+      <c r="H12" s="56" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
         </is>
       </c>
       <c r="I12" s="51" t="inlineStr">
         <is>
-          <t>Missing CC Vendor Name</t>
+          <t>Mismatched Category (Found: Meals &amp; Entertainment:Meals with clients)</t>
         </is>
       </c>
       <c r="J12" s="52" t="inlineStr">
         <is>
-          <t>Updated Name to 'Amex CC'</t>
+          <t>Reclassify to historical category: 'Dues &amp; subscriptions'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="50" t="n">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="B13" s="50" t="inlineStr">
         <is>
-          <t>07/28/2026</t>
+          <t>07/16/2026</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
@@ -1175,21 +1175,21 @@
       </c>
       <c r="D13" s="51" t="inlineStr">
         <is>
-          <t>Credit Card Credit</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E13" s="52" t="inlineStr">
         <is>
-          <t>Amex CC</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="F13" s="51" t="inlineStr">
         <is>
-          <t>AMEX Wireless Credit</t>
+          <t>ANTHROPIC* CLAUDE SUSAN FRANCISCO       CA</t>
         </is>
       </c>
       <c r="G13" s="53" t="n">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="H13" s="56" t="inlineStr">
         <is>
@@ -1198,27 +1198,27 @@
       </c>
       <c r="I13" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Utilities:Phone service)</t>
+          <t>Mismatched Category (Found: Office expenses:Software &amp; apps)</t>
         </is>
       </c>
       <c r="J13" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Amex CC'</t>
+          <t>Reclassify to historical category: 'Dues &amp; subscriptions'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="50" t="n">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="B14" s="50" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="C14" s="51" t="inlineStr">
         <is>
-          <t>BOA CC</t>
+          <t>Amex CC</t>
         </is>
       </c>
       <c r="D14" s="51" t="inlineStr">
@@ -1228,16 +1228,16 @@
       </c>
       <c r="E14" s="52" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Union 76</t>
         </is>
       </c>
       <c r="F14" s="51" t="inlineStr">
         <is>
-          <t>DD *DOORDASH HALALGYRO 8559731040 CA</t>
+          <t>UNION 76 09439498   FREMONT             CA</t>
         </is>
       </c>
       <c r="G14" s="53" t="n">
-        <v>35.85</v>
+        <v>105.17</v>
       </c>
       <c r="H14" s="56" t="inlineStr">
         <is>
@@ -1246,94 +1246,94 @@
       </c>
       <c r="I14" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Meals &amp; Entertainment:Entertainment)</t>
+          <t>Mismatched Category (Found: Gas And Fuel)</t>
         </is>
       </c>
       <c r="J14" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Meals &amp; Entertainment:Meals with clients'</t>
+          <t>Reclassify to historical category: 'Travel:Auto Expenses'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="50" t="n">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="B15" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>07/24/2026</t>
         </is>
       </c>
       <c r="C15" s="51" t="inlineStr">
         <is>
-          <t>BOA CC</t>
+          <t>Amex CC</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Credit Card Payment</t>
         </is>
       </c>
       <c r="E15" s="52" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Amex CC</t>
         </is>
       </c>
       <c r="F15" s="51" t="inlineStr">
         <is>
-          <t>DD *DOORDASH MASALAREP 8559731040 CA</t>
+          <t>AMERICAN EXPRESS DES:ACH PMT ID:W4206 INDN:SNEHA DATLA CO ID:1133133497 CCD</t>
         </is>
       </c>
       <c r="G15" s="53" t="n">
-        <v>27.41</v>
-      </c>
-      <c r="H15" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
+        <v>-4823.19</v>
+      </c>
+      <c r="H15" s="54" t="inlineStr">
+        <is>
+          <t>CC VENDOR UPDATED</t>
         </is>
       </c>
       <c r="I15" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Meals &amp; Entertainment:Entertainment)</t>
+          <t>Missing CC Vendor Name</t>
         </is>
       </c>
       <c r="J15" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Meals &amp; Entertainment:Meals with clients'</t>
+          <t>Set Vendor Name to 'Amex CC'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="50" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="B16" s="50" t="inlineStr">
         <is>
-          <t>07/13/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
-          <t>BOA CC</t>
+          <t>Amex CC</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Credit Card Credit</t>
         </is>
       </c>
       <c r="E16" s="52" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Amex CC</t>
         </is>
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
-          <t>OPENAI *CHATGPT SUBSCR 4158799686 CA</t>
+          <t>AMEX Wireless Credit</t>
         </is>
       </c>
       <c r="G16" s="53" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="H16" s="56" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       </c>
       <c r="I16" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Dues &amp; subscriptions)</t>
+          <t>Mismatched Category (Found: Utilities:Phone service)</t>
         </is>
       </c>
       <c r="J16" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Office expenses:Software &amp; apps'</t>
+          <t>Reclassify to historical category: 'Amex CC'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="50" t="n">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B17" s="50" t="inlineStr">
         <is>
-          <t>07/17/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
@@ -1377,11 +1377,11 @@
       </c>
       <c r="F17" s="51" t="inlineStr">
         <is>
-          <t>DD *DOORDASH ANGRYCHIC 8559731040 CA</t>
+          <t>DD *DOORDASH HALALGYRO 8559731040 CA</t>
         </is>
       </c>
       <c r="G17" s="53" t="n">
-        <v>26.1</v>
+        <v>35.85</v>
       </c>
       <c r="H17" s="56" t="inlineStr">
         <is>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="J17" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Meals &amp; Entertainment:Meals with clients'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="50" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B18" s="50" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C18" s="51" t="inlineStr">
@@ -1425,11 +1425,11 @@
       </c>
       <c r="F18" s="51" t="inlineStr">
         <is>
-          <t>DD *DOORDASH NAGASKITC 8559731040 CA</t>
+          <t>DD *DOORDASH MASALAREP 8559731040 CA</t>
         </is>
       </c>
       <c r="G18" s="53" t="n">
-        <v>31.21</v>
+        <v>27.41</v>
       </c>
       <c r="H18" s="56" t="inlineStr">
         <is>
@@ -1443,17 +1443,17 @@
       </c>
       <c r="J18" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Meals &amp; Entertainment:Meals with clients'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="50" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B19" s="50" t="inlineStr">
         <is>
-          <t>07/23/2026</t>
+          <t>07/17/2026</t>
         </is>
       </c>
       <c r="C19" s="51" t="inlineStr">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="F19" s="51" t="inlineStr">
         <is>
-          <t>DD *DOORDASH ULAVACHAR 8559731040 CA</t>
+          <t>DD *DOORDASH ANGRYCHIC 8559731040 CA</t>
         </is>
       </c>
       <c r="G19" s="53" t="n">
-        <v>17.98</v>
+        <v>26.1</v>
       </c>
       <c r="H19" s="56" t="inlineStr">
         <is>
@@ -1491,17 +1491,17 @@
       </c>
       <c r="J19" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Meals &amp; Entertainment:Meals with clients'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B20" s="50" t="inlineStr">
         <is>
-          <t>07/24/2026</t>
+          <t>07/20/2026</t>
         </is>
       </c>
       <c r="C20" s="51" t="inlineStr">
@@ -1511,45 +1511,45 @@
       </c>
       <c r="D20" s="51" t="inlineStr">
         <is>
-          <t>Credit Card Payment</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E20" s="52" t="inlineStr">
         <is>
-          <t>BOA CC</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F20" s="51" t="inlineStr">
         <is>
-          <t>BANK OF AMERICA - CREDIT CARD Bill Payment</t>
+          <t>DD *DOORDASH NAGASKITC 8559731040 CA</t>
         </is>
       </c>
       <c r="G20" s="53" t="n">
-        <v>-2965.7</v>
-      </c>
-      <c r="H20" s="54" t="inlineStr">
-        <is>
-          <t>CC VENDOR UPDATED</t>
+        <v>31.21</v>
+      </c>
+      <c r="H20" s="56" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
         </is>
       </c>
       <c r="I20" s="51" t="inlineStr">
         <is>
-          <t>Missing CC Vendor Name</t>
+          <t>Mismatched Category (Found: Meals &amp; Entertainment:Entertainment)</t>
         </is>
       </c>
       <c r="J20" s="52" t="inlineStr">
         <is>
-          <t>Updated Name to 'BOA CC'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="50" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B21" s="50" t="inlineStr">
         <is>
-          <t>07/26/2026</t>
+          <t>07/23/2026</t>
         </is>
       </c>
       <c r="C21" s="51" t="inlineStr">
@@ -1569,11 +1569,11 @@
       </c>
       <c r="F21" s="51" t="inlineStr">
         <is>
-          <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
+          <t>DD *DOORDASH ULAVACHAR 8559731040 CA</t>
         </is>
       </c>
       <c r="G21" s="53" t="n">
-        <v>24.94</v>
+        <v>17.98</v>
       </c>
       <c r="H21" s="56" t="inlineStr">
         <is>
@@ -1587,17 +1587,17 @@
       </c>
       <c r="J21" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Meals &amp; Entertainment:Meals with clients'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="50" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B22" s="50" t="inlineStr">
         <is>
-          <t>07/29/2026</t>
+          <t>07/24/2026</t>
         </is>
       </c>
       <c r="C22" s="51" t="inlineStr">
@@ -1607,69 +1607,69 @@
       </c>
       <c r="D22" s="51" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Credit Card Payment</t>
         </is>
       </c>
       <c r="E22" s="52" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>BOA CC</t>
         </is>
       </c>
       <c r="F22" s="51" t="inlineStr">
         <is>
-          <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
+          <t>BANK OF AMERICA - CREDIT CARD Bill Payment</t>
         </is>
       </c>
       <c r="G22" s="53" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H22" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
+        <v>-2965.7</v>
+      </c>
+      <c r="H22" s="54" t="inlineStr">
+        <is>
+          <t>CC VENDOR UPDATED</t>
         </is>
       </c>
       <c r="I22" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Meals &amp; Entertainment:Entertainment)</t>
+          <t>Missing CC Vendor Name</t>
         </is>
       </c>
       <c r="J22" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Meals &amp; Entertainment:Meals with clients'</t>
+          <t>Set Vendor Name to 'BOA CC'</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50" t="n">
-        <v>277</v>
+        <v>223</v>
       </c>
       <c r="B23" s="50" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>07/26/2026</t>
         </is>
       </c>
       <c r="C23" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>BOA CC</t>
         </is>
       </c>
       <c r="D23" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E23" s="52" t="inlineStr">
         <is>
-          <t>Medix Staffing Solutions, LLC,</t>
+          <t>Club 28 Badminton</t>
         </is>
       </c>
       <c r="F23" s="51" t="inlineStr">
         <is>
-          <t>Back-End Power BI Developer - 07/01/26 - 07/05/26</t>
+          <t>CLUB 28 BADMINTON DELE 9176316713 DE</t>
         </is>
       </c>
       <c r="G23" s="53" t="n">
-        <v>1336</v>
+        <v>140</v>
       </c>
       <c r="H23" s="56" t="inlineStr">
         <is>
@@ -1678,46 +1678,46 @@
       </c>
       <c r="I23" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Meals &amp; Entertainment:Meals with clients)</t>
         </is>
       </c>
       <c r="J23" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Owners Distribution'</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="n">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="B24" s="50" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>07/26/2026</t>
         </is>
       </c>
       <c r="C24" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>BOA CC</t>
         </is>
       </c>
       <c r="D24" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E24" s="52" t="inlineStr">
         <is>
-          <t>Medix Staffing Solutions, LLC,</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F24" s="51" t="inlineStr">
         <is>
-          <t>Back-End Power BI Developer - 07/06/26 - 07/12/26</t>
+          <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
         </is>
       </c>
       <c r="G24" s="53" t="n">
-        <v>3340</v>
+        <v>24.94</v>
       </c>
       <c r="H24" s="56" t="inlineStr">
         <is>
@@ -1726,46 +1726,46 @@
       </c>
       <c r="I24" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Meals &amp; Entertainment:Entertainment)</t>
         </is>
       </c>
       <c r="J24" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="n">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="B25" s="50" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/29/2026</t>
         </is>
       </c>
       <c r="C25" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>BOA CC</t>
         </is>
       </c>
       <c r="D25" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E25" s="52" t="inlineStr">
         <is>
-          <t>Medix Staffing Solutions, LLC,</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F25" s="51" t="inlineStr">
         <is>
-          <t>Back-End Power BI Developer - 07/13/26 - 07/19/26</t>
+          <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
         </is>
       </c>
       <c r="G25" s="53" t="n">
-        <v>3340</v>
+        <v>18.5</v>
       </c>
       <c r="H25" s="56" t="inlineStr">
         <is>
@@ -1774,94 +1774,94 @@
       </c>
       <c r="I25" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Meals &amp; Entertainment:Entertainment)</t>
         </is>
       </c>
       <c r="J25" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50" t="n">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="B26" s="50" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Uncategorized Income</t>
         </is>
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="E26" s="52" t="inlineStr">
         <is>
-          <t>Medix Staffing Solutions, LLC,</t>
+          <t>BKOFAMERICA MOBILE 07/29 3778024504</t>
         </is>
       </c>
       <c r="F26" s="51" t="inlineStr">
         <is>
-          <t>Back-End Power BI Developer - 07/19/26 - 07/25/26</t>
+          <t>BKOFAMERICA MOBILE 07/29 3778024504 DEPOSIT *MOBILE FL</t>
         </is>
       </c>
       <c r="G26" s="53" t="n">
-        <v>3340</v>
-      </c>
-      <c r="H26" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
+        <v>2803.69</v>
+      </c>
+      <c r="H26" s="55" t="inlineStr">
+        <is>
+          <t>UNCATEGORIZED</t>
         </is>
       </c>
       <c r="I26" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Uncategorized Transaction</t>
         </is>
       </c>
       <c r="J26" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Assign to specific client invoice or expense account</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50" t="n">
-        <v>281</v>
+        <v>321</v>
       </c>
       <c r="B27" s="50" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/31/2026</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consulting Fees</t>
         </is>
       </c>
       <c r="D27" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E27" s="52" t="inlineStr">
         <is>
-          <t>Medix Staffing Solutions, LLC,</t>
+          <t>Sage Solutions</t>
         </is>
       </c>
       <c r="F27" s="51" t="inlineStr">
         <is>
-          <t>Back-End Power BI Developer - 07/26/26 - 07/31/26</t>
+          <t>Venkata Vinay Kumar 07/01/2026 -07/31/2026 (88*$77)</t>
         </is>
       </c>
       <c r="G27" s="53" t="n">
-        <v>3340</v>
+        <v>6776</v>
       </c>
       <c r="H27" s="56" t="inlineStr">
         <is>
@@ -1870,46 +1870,46 @@
       </c>
       <c r="I27" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Consulting Fees)</t>
         </is>
       </c>
       <c r="J27" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Accounts Receivable (A/R)'</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50" t="n">
-        <v>282</v>
+        <v>363</v>
       </c>
       <c r="B28" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C28" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="D28" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E28" s="52" t="inlineStr">
         <is>
-          <t>Phoenix Staff Inc</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F28" s="51" t="inlineStr">
         <is>
-          <t>07/01/26 - 07/05/26</t>
+          <t>DD *DOORDASH HALALGYRO 8559731040 CA</t>
         </is>
       </c>
       <c r="G28" s="53" t="n">
-        <v>1104</v>
+        <v>35.85</v>
       </c>
       <c r="H28" s="56" t="inlineStr">
         <is>
@@ -1918,46 +1918,46 @@
       </c>
       <c r="I28" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Entertainment)</t>
         </is>
       </c>
       <c r="J28" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50" t="n">
-        <v>283</v>
+        <v>366</v>
       </c>
       <c r="B29" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C29" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="D29" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E29" s="52" t="inlineStr">
         <is>
-          <t>Phoenix Staff Inc</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F29" s="51" t="inlineStr">
         <is>
-          <t>07/06/26 - 07/12/26</t>
+          <t>DD *DOORDASH MASALAREP 8559731040 CA</t>
         </is>
       </c>
       <c r="G29" s="53" t="n">
-        <v>2760</v>
+        <v>27.41</v>
       </c>
       <c r="H29" s="56" t="inlineStr">
         <is>
@@ -1966,46 +1966,46 @@
       </c>
       <c r="I29" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Entertainment)</t>
         </is>
       </c>
       <c r="J29" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50" t="n">
-        <v>284</v>
+        <v>367</v>
       </c>
       <c r="B30" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/17/2026</t>
         </is>
       </c>
       <c r="C30" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="D30" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E30" s="52" t="inlineStr">
         <is>
-          <t>Phoenix Staff Inc</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F30" s="51" t="inlineStr">
         <is>
-          <t>07/13/26 - 07/19/26</t>
+          <t>DD *DOORDASH ANGRYCHIC 8559731040 CA</t>
         </is>
       </c>
       <c r="G30" s="53" t="n">
-        <v>2760</v>
+        <v>26.1</v>
       </c>
       <c r="H30" s="56" t="inlineStr">
         <is>
@@ -2014,46 +2014,46 @@
       </c>
       <c r="I30" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Entertainment)</t>
         </is>
       </c>
       <c r="J30" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50" t="n">
-        <v>285</v>
+        <v>368</v>
       </c>
       <c r="B31" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/20/2026</t>
         </is>
       </c>
       <c r="C31" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="D31" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E31" s="52" t="inlineStr">
         <is>
-          <t>Phoenix Staff Inc</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F31" s="51" t="inlineStr">
         <is>
-          <t>07/20/26 - 07/26/26</t>
+          <t>DD *DOORDASH NAGASKITC 8559731040 CA</t>
         </is>
       </c>
       <c r="G31" s="53" t="n">
-        <v>2600</v>
+        <v>31.21</v>
       </c>
       <c r="H31" s="56" t="inlineStr">
         <is>
@@ -2062,46 +2062,46 @@
       </c>
       <c r="I31" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Entertainment)</t>
         </is>
       </c>
       <c r="J31" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="n">
-        <v>286</v>
+        <v>369</v>
       </c>
       <c r="B32" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/23/2026</t>
         </is>
       </c>
       <c r="C32" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E32" s="52" t="inlineStr">
         <is>
-          <t>Phoenix Staff Inc</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F32" s="51" t="inlineStr">
         <is>
-          <t>07/27/26 - 07/31/26</t>
+          <t>DD *DOORDASH ULAVACHAR 8559731040 CA</t>
         </is>
       </c>
       <c r="G32" s="53" t="n">
-        <v>2600</v>
+        <v>17.98</v>
       </c>
       <c r="H32" s="56" t="inlineStr">
         <is>
@@ -2110,46 +2110,46 @@
       </c>
       <c r="I32" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Entertainment)</t>
         </is>
       </c>
       <c r="J32" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50" t="n">
-        <v>287</v>
+        <v>370</v>
       </c>
       <c r="B33" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/26/2026</t>
         </is>
       </c>
       <c r="C33" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E33" s="52" t="inlineStr">
         <is>
-          <t>SANA Software Solutions</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F33" s="51" t="inlineStr">
         <is>
-          <t>Nithya Tejasvini Baddam - July 2026</t>
+          <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
         </is>
       </c>
       <c r="G33" s="53" t="n">
-        <v>11440</v>
+        <v>24.94</v>
       </c>
       <c r="H33" s="56" t="inlineStr">
         <is>
@@ -2158,46 +2158,46 @@
       </c>
       <c r="I33" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Entertainment)</t>
         </is>
       </c>
       <c r="J33" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50" t="n">
-        <v>288</v>
+        <v>371</v>
       </c>
       <c r="B34" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/29/2026</t>
         </is>
       </c>
       <c r="C34" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="D34" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E34" s="52" t="inlineStr">
         <is>
-          <t>Nityo Infotech Corporation</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F34" s="51" t="inlineStr">
         <is>
-          <t>07/01/26 - 07/31/26</t>
+          <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
         </is>
       </c>
       <c r="G34" s="53" t="n">
-        <v>13024</v>
+        <v>18.5</v>
       </c>
       <c r="H34" s="56" t="inlineStr">
         <is>
@@ -2206,46 +2206,46 @@
       </c>
       <c r="I34" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Entertainment)</t>
         </is>
       </c>
       <c r="J34" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Meals &amp; Entertainment:Meals with clients'</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50" t="n">
-        <v>289</v>
+        <v>381</v>
       </c>
       <c r="B35" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C35" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Meals with clients</t>
         </is>
       </c>
       <c r="D35" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E35" s="52" t="inlineStr">
         <is>
-          <t>Nityo Infotech Corporation</t>
+          <t>AMK BLACKROCKWILMINGTON          DE</t>
         </is>
       </c>
       <c r="F35" s="51" t="inlineStr">
         <is>
-          <t>1.2% payment fee for Vendor Management Charges</t>
+          <t>AplPay AMK BLACKROCKWILMINGTON          DE</t>
         </is>
       </c>
       <c r="G35" s="53" t="n">
-        <v>-156.28</v>
+        <v>3.59</v>
       </c>
       <c r="H35" s="56" t="inlineStr">
         <is>
@@ -2254,46 +2254,46 @@
       </c>
       <c r="I35" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Meals with clients)</t>
         </is>
       </c>
       <c r="J35" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Dues &amp; subscriptions'</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50" t="n">
-        <v>290</v>
+        <v>398</v>
       </c>
       <c r="B36" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/26/2026</t>
         </is>
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Meals with clients</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E36" s="52" t="inlineStr">
         <is>
-          <t>Vivid Technologies Inc</t>
+          <t>Club 28 Badminton</t>
         </is>
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
-          <t>Professional Services from the period 07/01/26 - 07/31/26</t>
+          <t>CLUB 28 BADMINTON DELE 9176316713 DE</t>
         </is>
       </c>
       <c r="G36" s="53" t="n">
-        <v>10920</v>
+        <v>140</v>
       </c>
       <c r="H36" s="56" t="inlineStr">
         <is>
@@ -2302,46 +2302,46 @@
       </c>
       <c r="I36" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Meals with clients)</t>
         </is>
       </c>
       <c r="J36" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Owners Distribution'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50" t="n">
-        <v>291</v>
+        <v>418</v>
       </c>
       <c r="B37" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/16/2026</t>
         </is>
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Software &amp; apps</t>
         </is>
       </c>
       <c r="D37" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E37" s="52" t="inlineStr">
         <is>
-          <t>Bigbyte</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="F37" s="51" t="inlineStr">
         <is>
-          <t>Professional Services from the period 07/01/26 -07/31/26</t>
+          <t>ANTHROPIC* CLAUDE SUSAN FRANCISCO       CA</t>
         </is>
       </c>
       <c r="G37" s="53" t="n">
-        <v>11792</v>
+        <v>20</v>
       </c>
       <c r="H37" s="56" t="inlineStr">
         <is>
@@ -2350,46 +2350,46 @@
       </c>
       <c r="I37" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Software &amp; apps)</t>
         </is>
       </c>
       <c r="J37" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Dues &amp; subscriptions'</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50" t="n">
-        <v>292</v>
+        <v>446</v>
       </c>
       <c r="B38" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/20/2026</t>
         </is>
       </c>
       <c r="C38" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Building &amp; land rent</t>
         </is>
       </c>
       <c r="D38" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E38" s="52" t="inlineStr">
         <is>
-          <t>Randstand Digital</t>
+          <t>Exor Properties, LLC</t>
         </is>
       </c>
       <c r="F38" s="51" t="inlineStr">
         <is>
-          <t>Venkata Vinay Kumar 07/01/2026 -07/31/2026</t>
+          <t>Kindly schedule the monthly rental payment to be released on the 25th of each month</t>
         </is>
       </c>
       <c r="G38" s="53" t="n">
-        <v>7136.8</v>
+        <v>1650</v>
       </c>
       <c r="H38" s="56" t="inlineStr">
         <is>
@@ -2398,46 +2398,46 @@
       </c>
       <c r="I38" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Building &amp; land rent)</t>
         </is>
       </c>
       <c r="J38" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Accounts Payable (A/P)'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50" t="n">
-        <v>293</v>
+        <v>501</v>
       </c>
       <c r="B39" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="C39" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Phone service</t>
         </is>
       </c>
       <c r="D39" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Credit Card Credit</t>
         </is>
       </c>
       <c r="E39" s="52" t="inlineStr">
         <is>
-          <t>AGILISIUM CONSULTING LLC</t>
+          <t>Amex CC</t>
         </is>
       </c>
       <c r="F39" s="51" t="inlineStr">
         <is>
-          <t>Gadupudi Ravi Kumar – Professional Services for the period 07/01/26 - 07/31/26</t>
+          <t>AMEX Wireless Credit</t>
         </is>
       </c>
       <c r="G39" s="53" t="n">
-        <v>4048</v>
+        <v>-10</v>
       </c>
       <c r="H39" s="56" t="inlineStr">
         <is>
@@ -2446,46 +2446,46 @@
       </c>
       <c r="I39" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Phone service)</t>
         </is>
       </c>
       <c r="J39" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
+          <t>Reclassify to historical category: 'Amex CC'</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50" t="n">
-        <v>294</v>
+        <v>511</v>
       </c>
       <c r="B40" s="50" t="inlineStr">
         <is>
-          <t>07/31/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="C40" s="51" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Gas And Fuel</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E40" s="52" t="inlineStr">
         <is>
-          <t>Infinite Computer Solutions Inc.</t>
+          <t>Union 76</t>
         </is>
       </c>
       <c r="F40" s="51" t="inlineStr">
         <is>
-          <t>07/01/26 - 07/31/26 (Invoice I- 496082)</t>
+          <t>UNION 76 09439498   FREMONT             CA</t>
         </is>
       </c>
       <c r="G40" s="53" t="n">
-        <v>12414.48</v>
+        <v>105.17</v>
       </c>
       <c r="H40" s="56" t="inlineStr">
         <is>
@@ -2494,632 +2494,12 @@
       </c>
       <c r="I40" s="51" t="inlineStr">
         <is>
-          <t>Mismatched Category (Found: Services)</t>
+          <t>Mismatched Category (Found: Gas And Fuel)</t>
         </is>
       </c>
       <c r="J40" s="52" t="inlineStr">
         <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="50" t="n">
-        <v>295</v>
-      </c>
-      <c r="B41" s="50" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C41" s="51" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D41" s="51" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="E41" s="52" t="inlineStr">
-        <is>
-          <t>American Technology Services LLC</t>
-        </is>
-      </c>
-      <c r="F41" s="51" t="inlineStr">
-        <is>
-          <t>Nagendra Jaggarapu - 07/01/26 - 07/31/26 (Work Order# OMF-CW-0003240)</t>
-        </is>
-      </c>
-      <c r="G41" s="53" t="n">
-        <v>16800</v>
-      </c>
-      <c r="H41" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I41" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Services)</t>
-        </is>
-      </c>
-      <c r="J41" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="50" t="n">
-        <v>296</v>
-      </c>
-      <c r="B42" s="50" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C42" s="51" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D42" s="51" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="E42" s="52" t="inlineStr">
-        <is>
-          <t>Sage Solutions LLC</t>
-        </is>
-      </c>
-      <c r="F42" s="51" t="inlineStr">
-        <is>
-          <t>Sravan Tadepalli_07/01/26- 07/31/26</t>
-        </is>
-      </c>
-      <c r="G42" s="53" t="n">
-        <v>11264</v>
-      </c>
-      <c r="H42" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I42" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Services)</t>
-        </is>
-      </c>
-      <c r="J42" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Consulting Fees'</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="50" t="n">
-        <v>297</v>
-      </c>
-      <c r="B43" s="50" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C43" s="51" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D43" s="51" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="E43" s="52" t="inlineStr">
-        <is>
-          <t>American Technology Services LLC</t>
-        </is>
-      </c>
-      <c r="F43" s="51" t="inlineStr">
-        <is>
-          <t>Professional Services from the period 07/01/26 - 07/31/26 (Work Order# OMF-WO-0003012)</t>
-        </is>
-      </c>
-      <c r="G43" s="53" t="n">
-        <v>11440</v>
-      </c>
-      <c r="H43" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I43" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Services)</t>
-        </is>
-      </c>
-      <c r="J43" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="50" t="n">
-        <v>298</v>
-      </c>
-      <c r="B44" s="50" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C44" s="51" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D44" s="51" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="E44" s="52" t="inlineStr">
-        <is>
-          <t>AGILISIUM CONSULTING LLC</t>
-        </is>
-      </c>
-      <c r="F44" s="51" t="inlineStr">
-        <is>
-          <t>Rakesh Varma Uppalapati _ 07/01/26 - 07/31/26</t>
-        </is>
-      </c>
-      <c r="G44" s="53" t="n">
-        <v>14960</v>
-      </c>
-      <c r="H44" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I44" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Services)</t>
-        </is>
-      </c>
-      <c r="J44" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="50" t="n">
-        <v>299</v>
-      </c>
-      <c r="B45" s="50" t="inlineStr">
-        <is>
-          <t>07/31/2026</t>
-        </is>
-      </c>
-      <c r="C45" s="51" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D45" s="51" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="E45" s="52" t="inlineStr">
-        <is>
-          <t>Vendorpass, INC</t>
-        </is>
-      </c>
-      <c r="F45" s="51" t="inlineStr">
-        <is>
-          <t>07/01/26-07/31/26</t>
-        </is>
-      </c>
-      <c r="G45" s="53" t="n">
-        <v>9328</v>
-      </c>
-      <c r="H45" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I45" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Services)</t>
-        </is>
-      </c>
-      <c r="J45" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Receivable (A/R)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="50" t="n">
-        <v>302</v>
-      </c>
-      <c r="B46" s="50" t="inlineStr">
-        <is>
-          <t>07/28/2026</t>
-        </is>
-      </c>
-      <c r="C46" s="51" t="inlineStr">
-        <is>
-          <t>Uncategorized Income</t>
-        </is>
-      </c>
-      <c r="D46" s="51" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="E46" s="52" t="inlineStr">
-        <is>
-          <t>BKOFAMERICA MOBILE 07/29 37780</t>
-        </is>
-      </c>
-      <c r="F46" s="51" t="inlineStr">
-        <is>
-          <t>BKOFAMERICA MOBILE 07/29 3778024504 DEPOSIT *MOBILE FL</t>
-        </is>
-      </c>
-      <c r="G46" s="53" t="n">
-        <v>2803.69</v>
-      </c>
-      <c r="H46" s="55" t="inlineStr">
-        <is>
-          <t>UNCATEGORIZED</t>
-        </is>
-      </c>
-      <c r="I46" s="51" t="inlineStr">
-        <is>
-          <t>Uncategorized Transaction</t>
-        </is>
-      </c>
-      <c r="J46" s="52" t="inlineStr">
-        <is>
-          <t>Assign to specific client invoice or expense account</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="50" t="n">
-        <v>306</v>
-      </c>
-      <c r="B47" s="50" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="C47" s="51" t="inlineStr">
-        <is>
-          <t>COGS - Vendor</t>
-        </is>
-      </c>
-      <c r="D47" s="51" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E47" s="52" t="inlineStr">
-        <is>
-          <t>Astramind Solutions Private Limited</t>
-        </is>
-      </c>
-      <c r="F47" s="51" t="inlineStr">
-        <is>
-          <t>Offshore IT Support Services - June 2026</t>
-        </is>
-      </c>
-      <c r="G47" s="53" t="n">
-        <v>12675.9</v>
-      </c>
-      <c r="H47" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I47" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: COGS - Vendor)</t>
-        </is>
-      </c>
-      <c r="J47" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Payable (A/P)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="50" t="n">
-        <v>307</v>
-      </c>
-      <c r="B48" s="50" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="C48" s="51" t="inlineStr">
-        <is>
-          <t>COGS - Vendor</t>
-        </is>
-      </c>
-      <c r="D48" s="51" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E48" s="52" t="inlineStr">
-        <is>
-          <t>Astramind Solutions Private Limited</t>
-        </is>
-      </c>
-      <c r="F48" s="51" t="inlineStr">
-        <is>
-          <t>Offshore marketing and web development services - ₹9,02,720.00</t>
-        </is>
-      </c>
-      <c r="G48" s="53" t="n">
-        <v>9541.690000000001</v>
-      </c>
-      <c r="H48" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I48" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: COGS - Vendor)</t>
-        </is>
-      </c>
-      <c r="J48" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Payable (A/P)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="50" t="n">
-        <v>308</v>
-      </c>
-      <c r="B49" s="50" t="inlineStr">
-        <is>
-          <t>07/22/2026</t>
-        </is>
-      </c>
-      <c r="C49" s="51" t="inlineStr">
-        <is>
-          <t>COGS - Vendor</t>
-        </is>
-      </c>
-      <c r="D49" s="51" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E49" s="52" t="inlineStr">
-        <is>
-          <t>Aneru LLC</t>
-        </is>
-      </c>
-      <c r="F49" s="51" t="inlineStr"/>
-      <c r="G49" s="53" t="n">
-        <v>15556</v>
-      </c>
-      <c r="H49" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I49" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: COGS - Vendor)</t>
-        </is>
-      </c>
-      <c r="J49" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Payable (A/P)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="50" t="n">
-        <v>309</v>
-      </c>
-      <c r="B50" s="50" t="inlineStr">
-        <is>
-          <t>07/28/2026</t>
-        </is>
-      </c>
-      <c r="C50" s="51" t="inlineStr">
-        <is>
-          <t>COGS - Vendor</t>
-        </is>
-      </c>
-      <c r="D50" s="51" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E50" s="52" t="inlineStr">
-        <is>
-          <t>PTL Consultancy</t>
-        </is>
-      </c>
-      <c r="F50" s="51" t="inlineStr">
-        <is>
-          <t>India July 2026 Salaries -  SUBTOTAL INR 528,875.00</t>
-        </is>
-      </c>
-      <c r="G50" s="53" t="n">
-        <v>5546.55</v>
-      </c>
-      <c r="H50" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I50" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: COGS - Vendor)</t>
-        </is>
-      </c>
-      <c r="J50" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Accounts Payable (A/P)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="50" t="n">
-        <v>329</v>
-      </c>
-      <c r="B51" s="50" t="inlineStr">
-        <is>
-          <t>07/13/2026</t>
-        </is>
-      </c>
-      <c r="C51" s="51" t="inlineStr">
-        <is>
-          <t>Dues &amp; subscriptions</t>
-        </is>
-      </c>
-      <c r="D51" s="51" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E51" s="52" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="F51" s="51" t="inlineStr">
-        <is>
-          <t>OPENAI *CHATGPT SUBSCR 4158799686 CA</t>
-        </is>
-      </c>
-      <c r="G51" s="53" t="n">
-        <v>20</v>
-      </c>
-      <c r="H51" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I51" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Dues &amp; subscriptions)</t>
-        </is>
-      </c>
-      <c r="J51" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Office expenses:Software &amp; apps'</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="50" t="n">
-        <v>406</v>
-      </c>
-      <c r="B52" s="50" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C52" s="51" t="inlineStr">
-        <is>
-          <t>Office supplies</t>
-        </is>
-      </c>
-      <c r="D52" s="51" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E52" s="52" t="inlineStr">
-        <is>
-          <t>Banner Pest Services</t>
-        </is>
-      </c>
-      <c r="F52" s="51" t="inlineStr">
-        <is>
-          <t>PY *BANNER PEST SERVSAN JOSE            CA</t>
-        </is>
-      </c>
-      <c r="G52" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="H52" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I52" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Office supplies)</t>
-        </is>
-      </c>
-      <c r="J52" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Repairs &amp; maintenance'</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="50" t="n">
-        <v>501</v>
-      </c>
-      <c r="B53" s="50" t="inlineStr">
-        <is>
-          <t>07/28/2026</t>
-        </is>
-      </c>
-      <c r="C53" s="51" t="inlineStr">
-        <is>
-          <t>Phone service</t>
-        </is>
-      </c>
-      <c r="D53" s="51" t="inlineStr">
-        <is>
-          <t>Credit Card Credit</t>
-        </is>
-      </c>
-      <c r="E53" s="52" t="inlineStr">
-        <is>
-          <t>Amex CC</t>
-        </is>
-      </c>
-      <c r="F53" s="51" t="inlineStr">
-        <is>
-          <t>AMEX Wireless Credit</t>
-        </is>
-      </c>
-      <c r="G53" s="53" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H53" s="56" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="I53" s="51" t="inlineStr">
-        <is>
-          <t>Mismatched Category (Found: Phone service)</t>
-        </is>
-      </c>
-      <c r="J53" s="52" t="inlineStr">
-        <is>
-          <t>Reclassify to 'Amex CC'</t>
+          <t>Reclassify to historical category: 'Travel:Auto Expenses'</t>
         </is>
       </c>
     </row>
@@ -3299,7 +2679,7 @@
       </c>
       <c r="L8" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: 401K Payable</t>
+          <t>Verified: 401K Payable</t>
         </is>
       </c>
     </row>
@@ -3348,7 +2728,7 @@
       </c>
       <c r="L9" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -3397,7 +2777,7 @@
       </c>
       <c r="L10" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -3442,7 +2822,7 @@
       </c>
       <c r="L11" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -3487,7 +2867,7 @@
       </c>
       <c r="L12" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -3532,7 +2912,7 @@
       </c>
       <c r="L13" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -3577,7 +2957,7 @@
       </c>
       <c r="L14" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3002,7 @@
       </c>
       <c r="L15" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3051,7 @@
       </c>
       <c r="L16" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3096,7 @@
       </c>
       <c r="L17" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3141,7 @@
       </c>
       <c r="L18" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3186,7 @@
       </c>
       <c r="L19" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3235,7 @@
       </c>
       <c r="L20" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Immigration Expenses</t>
+          <t>Verified: Immigration Expenses</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3284,7 @@
       </c>
       <c r="L21" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3333,7 @@
       </c>
       <c r="L22" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3378,7 @@
       </c>
       <c r="L23" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4088,7 +3468,7 @@
       </c>
       <c r="L25" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll wages and tax to pay:Payroll tax to pay</t>
+          <t>Verified: Payroll tax to pay</t>
         </is>
       </c>
     </row>
@@ -4133,7 +3513,7 @@
       </c>
       <c r="L26" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Payroll Wages Payable</t>
         </is>
       </c>
     </row>
@@ -4178,7 +3558,7 @@
       </c>
       <c r="L27" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4223,7 +3603,7 @@
       </c>
       <c r="L28" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4313,7 +3693,7 @@
       </c>
       <c r="L30" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: 401K Payable</t>
+          <t>Verified: 401K Payable</t>
         </is>
       </c>
     </row>
@@ -4362,7 +3742,7 @@
       </c>
       <c r="L31" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -4407,7 +3787,7 @@
       </c>
       <c r="L32" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4456,7 +3836,7 @@
       </c>
       <c r="L33" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4501,7 +3881,7 @@
       </c>
       <c r="L34" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4546,7 +3926,7 @@
       </c>
       <c r="L35" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4016,7 @@
       </c>
       <c r="L37" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4061,7 @@
       </c>
       <c r="L38" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4106,7 @@
       </c>
       <c r="L39" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: General business expenses:Bank fees &amp; service charges</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4151,7 @@
       </c>
       <c r="L40" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Consulting Fees</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4200,7 @@
       </c>
       <c r="L41" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4245,7 @@
       </c>
       <c r="L42" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4290,7 @@
       </c>
       <c r="L43" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll wages and tax to pay:Payroll tax to pay</t>
+          <t>Verified: Payroll tax to pay</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4335,7 @@
       </c>
       <c r="L44" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -5004,7 +4384,7 @@
       </c>
       <c r="L45" s="65" t="inlineStr">
         <is>
-          <t>Vendor Name set to 'Amex CC'</t>
+          <t>Vendor Name auto-set to 'Amex CC'</t>
         </is>
       </c>
     </row>
@@ -5049,7 +4429,7 @@
       </c>
       <c r="L46" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Payroll Wages Payable</t>
         </is>
       </c>
     </row>
@@ -5098,7 +4478,7 @@
       </c>
       <c r="L47" s="65" t="inlineStr">
         <is>
-          <t>Vendor Name set to 'BOA CC'</t>
+          <t>Vendor Name auto-set to 'BOA CC'</t>
         </is>
       </c>
     </row>
@@ -5147,7 +4527,7 @@
       </c>
       <c r="L48" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -5237,7 +4617,7 @@
       </c>
       <c r="L50" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Services</t>
         </is>
       </c>
     </row>
@@ -5282,7 +4662,7 @@
       </c>
       <c r="L51" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Immigration Expenses</t>
+          <t>Verified: Immigration Expenses</t>
         </is>
       </c>
     </row>
@@ -5327,7 +4707,7 @@
       </c>
       <c r="L52" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Consulting Fees</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -5372,7 +4752,7 @@
       </c>
       <c r="L53" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5417,7 +4797,7 @@
       </c>
       <c r="L54" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Payroll Wages Payable</t>
         </is>
       </c>
     </row>
@@ -5462,7 +4842,7 @@
       </c>
       <c r="L55" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll wages and tax to pay:Payroll tax to pay</t>
+          <t>Verified: Payroll tax to pay</t>
         </is>
       </c>
     </row>
@@ -5507,7 +4887,7 @@
       </c>
       <c r="L56" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5552,7 +4932,7 @@
       </c>
       <c r="L57" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5597,7 +4977,7 @@
       </c>
       <c r="L58" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5022,7 @@
       </c>
       <c r="L59" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5067,7 @@
       </c>
       <c r="L60" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5112,7 @@
       </c>
       <c r="L61" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5185,7 @@
       </c>
       <c r="L65" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5230,7 @@
       </c>
       <c r="L66" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5275,7 @@
       </c>
       <c r="L67" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5324,7 @@
       </c>
       <c r="L68" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5369,7 @@
       </c>
       <c r="L69" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6034,7 +5414,7 @@
       </c>
       <c r="L70" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6079,7 +5459,7 @@
       </c>
       <c r="L71" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6128,7 +5508,7 @@
       </c>
       <c r="L72" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6173,7 +5553,7 @@
       </c>
       <c r="L73" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6218,7 +5598,7 @@
       </c>
       <c r="L74" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6263,7 +5643,7 @@
       </c>
       <c r="L75" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6308,7 +5688,7 @@
       </c>
       <c r="L76" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +5737,7 @@
       </c>
       <c r="L77" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6402,7 +5782,7 @@
       </c>
       <c r="L78" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6451,7 +5831,7 @@
       </c>
       <c r="L79" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6496,7 +5876,7 @@
       </c>
       <c r="L80" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6541,7 +5921,7 @@
       </c>
       <c r="L81" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Consulting Fees</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6590,7 +5970,7 @@
       </c>
       <c r="L82" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6015,7 @@
       </c>
       <c r="L83" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6060,7 @@
       </c>
       <c r="L84" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Services</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6105,7 @@
       </c>
       <c r="L85" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6150,7 @@
       </c>
       <c r="L86" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6199,7 @@
       </c>
       <c r="L87" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6244,7 @@
       </c>
       <c r="L88" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6289,7 @@
       </c>
       <c r="L89" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6342,7 @@
       </c>
       <c r="L90" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7011,7 +6391,7 @@
       </c>
       <c r="L91" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7064,7 +6444,7 @@
       </c>
       <c r="L92" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7117,7 +6497,7 @@
       </c>
       <c r="L93" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7170,7 +6550,7 @@
       </c>
       <c r="L94" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7223,7 +6603,7 @@
       </c>
       <c r="L95" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7276,7 +6656,7 @@
       </c>
       <c r="L96" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7329,7 +6709,7 @@
       </c>
       <c r="L97" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7382,7 +6762,7 @@
       </c>
       <c r="L98" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Consulting Fees</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7435,7 +6815,7 @@
       </c>
       <c r="L99" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7488,7 +6868,7 @@
       </c>
       <c r="L100" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7533,7 +6913,7 @@
       </c>
       <c r="L101" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7586,7 +6966,7 @@
       </c>
       <c r="L102" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Receivable (A/R)</t>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7183,7 @@
       </c>
       <c r="L121" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7232,7 @@
       </c>
       <c r="L122" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7285,7 @@
       </c>
       <c r="L123" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7334,7 @@
       </c>
       <c r="L124" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8007,7 +7387,7 @@
       </c>
       <c r="L125" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8056,7 +7436,7 @@
       </c>
       <c r="L126" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8105,7 +7485,7 @@
       </c>
       <c r="L127" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8150,7 +7530,7 @@
       </c>
       <c r="L128" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8195,7 +7575,7 @@
       </c>
       <c r="L129" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8244,7 +7624,7 @@
       </c>
       <c r="L130" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8289,7 +7669,7 @@
       </c>
       <c r="L131" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8342,7 +7722,7 @@
       </c>
       <c r="L132" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8391,7 +7771,7 @@
       </c>
       <c r="L133" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Accounts Payable (A/P)</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8436,7 +7816,7 @@
       </c>
       <c r="L134" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Consulting Fees</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -8485,60 +7865,60 @@
       </c>
       <c r="L135" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Consulting Fees</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
     <row r="136" ht="16" customHeight="1">
-      <c r="B136" s="58" t="inlineStr">
+      <c r="B136" s="71" t="inlineStr">
         <is>
           <t>Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="C136" s="58" t="inlineStr">
+      <c r="C136" s="71" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D136" s="58" t="inlineStr">
+      <c r="D136" s="71" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E136" s="58" t="inlineStr">
+      <c r="E136" s="71" t="inlineStr">
         <is>
           <t>12282018626</t>
         </is>
       </c>
-      <c r="F136" s="58" t="inlineStr">
+      <c r="F136" s="71" t="inlineStr">
         <is>
           <t>Sage Solutions</t>
         </is>
       </c>
-      <c r="G136" s="58" t="inlineStr">
+      <c r="G136" s="71" t="inlineStr">
         <is>
           <t>Venkata Vinay Kumar 07/01/2026 -07/31/2026 (88*$77)</t>
         </is>
       </c>
-      <c r="H136" s="58" t="inlineStr">
+      <c r="H136" s="71" t="inlineStr">
         <is>
           <t>Consulting Fees</t>
         </is>
       </c>
-      <c r="I136" s="59" t="n">
+      <c r="I136" s="72" t="n">
         <v>6776</v>
       </c>
-      <c r="J136" s="59" t="n">
+      <c r="J136" s="72" t="n">
         <v>113269.42</v>
       </c>
-      <c r="K136" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L136" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Consulting Fees</t>
+      <c r="K136" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L136" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Accounts Receivable (A/R)' based on historical data, found 'Accounts Payable (A/P)'.</t>
         </is>
       </c>
     </row>
@@ -8611,7 +7991,7 @@
       </c>
       <c r="L140" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Interest paid</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8036,7 @@
       </c>
       <c r="L141" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Shareholders' equity:Distributions</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8081,7 @@
       </c>
       <c r="L142" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Other</t>
+          <t>Verified: Utilities:Other</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8126,7 @@
       </c>
       <c r="L143" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Vehicle expenses:Parking &amp; tolls</t>
+          <t>Verified: Vehicle expenses:Parking &amp; tolls</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8171,7 @@
       </c>
       <c r="L144" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: General business expenses:Memberships &amp; subscriptions</t>
+          <t>Verified: General business expenses:Memberships &amp; subscriptions</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8261,7 @@
       </c>
       <c r="L146" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -9061,52 +8441,52 @@
       </c>
       <c r="L150" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Gas And Fuel</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
     <row r="151" ht="16" customHeight="1">
-      <c r="B151" s="58" t="inlineStr">
+      <c r="B151" s="71" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="C151" s="58" t="inlineStr">
+      <c r="C151" s="71" t="inlineStr">
         <is>
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="D151" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E151" s="58" t="inlineStr"/>
-      <c r="F151" s="58" t="inlineStr"/>
-      <c r="G151" s="58" t="inlineStr">
+      <c r="D151" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E151" s="71" t="inlineStr"/>
+      <c r="F151" s="71" t="inlineStr"/>
+      <c r="G151" s="71" t="inlineStr">
         <is>
           <t>AplPay AMK BLACKROCKWILMINGTON          DE</t>
         </is>
       </c>
-      <c r="H151" s="58" t="inlineStr">
+      <c r="H151" s="71" t="inlineStr">
         <is>
           <t>Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
-      <c r="I151" s="59" t="n">
+      <c r="I151" s="72" t="n">
         <v>3.59</v>
       </c>
-      <c r="J151" s="59" t="n">
+      <c r="J151" s="72" t="n">
         <v>5445.499999999999</v>
       </c>
-      <c r="K151" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L151" s="61" t="inlineStr">
-        <is>
-          <t>Standard ledger entry</t>
+      <c r="K151" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L151" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Dues &amp; subscriptions' based on historical data, found 'Meals &amp; Entertainment:Meals with clients'.</t>
         </is>
       </c>
     </row>
@@ -9151,7 +8531,7 @@
       </c>
       <c r="L152" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Dues &amp; subscriptions</t>
+          <t>Verified: Dues &amp; subscriptions</t>
         </is>
       </c>
     </row>
@@ -9196,52 +8576,52 @@
       </c>
       <c r="L153" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
     <row r="154" ht="16" customHeight="1">
-      <c r="B154" s="71" t="inlineStr">
+      <c r="B154" s="58" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="C154" s="71" t="inlineStr">
+      <c r="C154" s="58" t="inlineStr">
         <is>
           <t>07/10/2026</t>
         </is>
       </c>
-      <c r="D154" s="71" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E154" s="71" t="inlineStr"/>
-      <c r="F154" s="71" t="inlineStr"/>
-      <c r="G154" s="71" t="inlineStr">
+      <c r="D154" s="58" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E154" s="58" t="inlineStr"/>
+      <c r="F154" s="58" t="inlineStr"/>
+      <c r="G154" s="58" t="inlineStr">
         <is>
           <t>PY *BANNER PEST SERVSAN JOSE            CA</t>
         </is>
       </c>
-      <c r="H154" s="71" t="inlineStr">
+      <c r="H154" s="58" t="inlineStr">
         <is>
           <t>Office expenses:Office supplies</t>
         </is>
       </c>
-      <c r="I154" s="72" t="n">
+      <c r="I154" s="59" t="n">
         <v>150</v>
       </c>
-      <c r="J154" s="72" t="n">
+      <c r="J154" s="59" t="n">
         <v>5701.629999999999</v>
       </c>
-      <c r="K154" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L154" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Repairs &amp; maintenance', found 'Office expenses:Office supplies'.</t>
+      <c r="K154" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L154" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -9331,7 +8711,7 @@
       </c>
       <c r="L156" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Insurance</t>
+          <t>Verified: Insurance</t>
         </is>
       </c>
     </row>
@@ -9376,7 +8756,7 @@
       </c>
       <c r="L157" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Insurance</t>
+          <t>Verified: Insurance</t>
         </is>
       </c>
     </row>
@@ -9421,7 +8801,7 @@
       </c>
       <c r="L158" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: General business expenses:Memberships &amp; subscriptions</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -9466,7 +8846,7 @@
       </c>
       <c r="L159" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: General business expenses:Memberships &amp; subscriptions</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9026,7 @@
       </c>
       <c r="L163" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9116,7 @@
       </c>
       <c r="L165" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9161,7 @@
       </c>
       <c r="L166" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
@@ -9831,47 +9211,47 @@
       </c>
     </row>
     <row r="168" ht="16" customHeight="1">
-      <c r="B168" s="58" t="inlineStr">
+      <c r="B168" s="71" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="C168" s="58" t="inlineStr">
+      <c r="C168" s="71" t="inlineStr">
         <is>
           <t>07/16/2026</t>
         </is>
       </c>
-      <c r="D168" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E168" s="58" t="inlineStr"/>
-      <c r="F168" s="58" t="inlineStr"/>
-      <c r="G168" s="58" t="inlineStr">
+      <c r="D168" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E168" s="71" t="inlineStr"/>
+      <c r="F168" s="71" t="inlineStr"/>
+      <c r="G168" s="71" t="inlineStr">
         <is>
           <t>ANTHROPIC* CLAUDE SUSAN FRANCISCO       CA</t>
         </is>
       </c>
-      <c r="H168" s="58" t="inlineStr">
+      <c r="H168" s="71" t="inlineStr">
         <is>
           <t>Office expenses:Software &amp; apps</t>
         </is>
       </c>
-      <c r="I168" s="59" t="n">
+      <c r="I168" s="72" t="n">
         <v>20</v>
       </c>
-      <c r="J168" s="59" t="n">
+      <c r="J168" s="72" t="n">
         <v>7464.389999999999</v>
       </c>
-      <c r="K168" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L168" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+      <c r="K168" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L168" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Dues &amp; subscriptions' based on historical data, found 'Office expenses:Software &amp; apps'.</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9296,7 @@
       </c>
       <c r="L169" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Vehicle expenses:Parking &amp; tolls</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -10006,7 +9386,7 @@
       </c>
       <c r="L171" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -10051,7 +9431,7 @@
       </c>
       <c r="L172" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -10096,7 +9476,7 @@
       </c>
       <c r="L173" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -10141,7 +9521,7 @@
       </c>
       <c r="L174" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -10186,52 +9566,52 @@
       </c>
       <c r="L175" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Vehicle expenses:Parking &amp; tolls</t>
+          <t>Verified: Vehicle expenses:Parking &amp; tolls</t>
         </is>
       </c>
     </row>
     <row r="176" ht="16" customHeight="1">
-      <c r="B176" s="58" t="inlineStr">
+      <c r="B176" s="71" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="C176" s="58" t="inlineStr">
+      <c r="C176" s="71" t="inlineStr">
         <is>
           <t>07/18/2026</t>
         </is>
       </c>
-      <c r="D176" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E176" s="58" t="inlineStr"/>
-      <c r="F176" s="58" t="inlineStr"/>
-      <c r="G176" s="58" t="inlineStr">
+      <c r="D176" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E176" s="71" t="inlineStr"/>
+      <c r="F176" s="71" t="inlineStr"/>
+      <c r="G176" s="71" t="inlineStr">
         <is>
           <t>UNION 76 09439498   FREMONT             CA</t>
         </is>
       </c>
-      <c r="H176" s="58" t="inlineStr">
+      <c r="H176" s="71" t="inlineStr">
         <is>
           <t>Gas And Fuel</t>
         </is>
       </c>
-      <c r="I176" s="59" t="n">
+      <c r="I176" s="72" t="n">
         <v>105.17</v>
       </c>
-      <c r="J176" s="59" t="n">
+      <c r="J176" s="72" t="n">
         <v>7851.879999999999</v>
       </c>
-      <c r="K176" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L176" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Gas And Fuel</t>
+      <c r="K176" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L176" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Travel:Auto Expenses' based on historical data, found 'Gas And Fuel'.</t>
         </is>
       </c>
     </row>
@@ -10321,7 +9701,7 @@
       </c>
       <c r="L178" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -10366,7 +9746,7 @@
       </c>
       <c r="L179" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
@@ -10411,7 +9791,7 @@
       </c>
       <c r="L180" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -10456,7 +9836,7 @@
       </c>
       <c r="L181" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -10501,7 +9881,7 @@
       </c>
       <c r="L182" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10016,7 @@
       </c>
       <c r="L185" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Office supplies</t>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10061,7 @@
       </c>
       <c r="L186" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Insurance</t>
+          <t>Verified: Insurance</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10106,7 @@
       </c>
       <c r="L187" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Electricity</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10200,7 @@
       </c>
       <c r="L189" s="65" t="inlineStr">
         <is>
-          <t>Vendor Name set to 'Amex CC'</t>
+          <t>Vendor Name auto-set to 'Amex CC'</t>
         </is>
       </c>
     </row>
@@ -11000,7 +10380,7 @@
       </c>
       <c r="L193" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -11045,7 +10425,7 @@
       </c>
       <c r="L194" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+          <t>Verified: Office expenses:Software &amp; apps</t>
         </is>
       </c>
     </row>
@@ -11090,7 +10470,7 @@
       </c>
       <c r="L195" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Amex CC', found 'Utilities:Phone service'.</t>
+          <t>Expected 'Amex CC' based on historical data, found 'Utilities:Phone service'.</t>
         </is>
       </c>
     </row>
@@ -11180,7 +10560,7 @@
       </c>
       <c r="L197" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Gas And Fuel</t>
+          <t>Verified: Gas And Fuel</t>
         </is>
       </c>
     </row>
@@ -11225,7 +10605,7 @@
       </c>
       <c r="L198" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -11315,7 +10695,7 @@
       </c>
       <c r="L200" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
@@ -11360,7 +10740,7 @@
       </c>
       <c r="L201" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -11405,7 +10785,7 @@
       </c>
       <c r="L202" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -11478,7 +10858,7 @@
       </c>
       <c r="L206" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -11523,7 +10903,7 @@
       </c>
       <c r="L207" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+          <t>Verified: Office expenses:Software &amp; apps</t>
         </is>
       </c>
     </row>
@@ -11568,7 +10948,7 @@
       </c>
       <c r="L208" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11038,7 @@
       </c>
       <c r="L210" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Meals &amp; Entertainment:Meals with clients', found 'Meals &amp; Entertainment:Entertainment'.</t>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Meals &amp; Entertainment:Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11083,7 @@
       </c>
       <c r="L211" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11128,7 @@
       </c>
       <c r="L212" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11173,7 @@
       </c>
       <c r="L213" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -11838,52 +11218,52 @@
       </c>
       <c r="L214" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Meals &amp; Entertainment:Meals with clients', found 'Meals &amp; Entertainment:Entertainment'.</t>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Meals &amp; Entertainment:Entertainment'.</t>
         </is>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1">
-      <c r="B215" s="71" t="inlineStr">
+      <c r="B215" s="58" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="C215" s="71" t="inlineStr">
+      <c r="C215" s="58" t="inlineStr">
         <is>
           <t>07/13/2026</t>
         </is>
       </c>
-      <c r="D215" s="71" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E215" s="71" t="inlineStr"/>
-      <c r="F215" s="71" t="inlineStr"/>
-      <c r="G215" s="71" t="inlineStr">
+      <c r="D215" s="58" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E215" s="58" t="inlineStr"/>
+      <c r="F215" s="58" t="inlineStr"/>
+      <c r="G215" s="58" t="inlineStr">
         <is>
           <t>OPENAI *CHATGPT SUBSCR 4158799686 CA</t>
         </is>
       </c>
-      <c r="H215" s="71" t="inlineStr">
+      <c r="H215" s="58" t="inlineStr">
         <is>
           <t>Dues &amp; subscriptions</t>
         </is>
       </c>
-      <c r="I215" s="72" t="n">
+      <c r="I215" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="J215" s="72" t="n">
+      <c r="J215" s="59" t="n">
         <v>3294.72</v>
       </c>
-      <c r="K215" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L215" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Office expenses:Software &amp; apps', found 'Dues &amp; subscriptions'.</t>
+      <c r="K215" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L215" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Dues &amp; subscriptions</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11308,7 @@
       </c>
       <c r="L216" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Office supplies</t>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11353,7 @@
       </c>
       <c r="L217" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Office supplies</t>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -12018,7 +11398,7 @@
       </c>
       <c r="L218" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Meals &amp; Entertainment:Meals with clients', found 'Meals &amp; Entertainment:Entertainment'.</t>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Meals &amp; Entertainment:Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -12063,7 +11443,7 @@
       </c>
       <c r="L219" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -12108,7 +11488,7 @@
       </c>
       <c r="L220" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Meals &amp; Entertainment:Meals with clients', found 'Meals &amp; Entertainment:Entertainment'.</t>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Meals &amp; Entertainment:Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -12153,7 +11533,7 @@
       </c>
       <c r="L221" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Meals &amp; Entertainment:Meals with clients', found 'Meals &amp; Entertainment:Entertainment'.</t>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Meals &amp; Entertainment:Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -12202,52 +11582,52 @@
       </c>
       <c r="L222" s="65" t="inlineStr">
         <is>
-          <t>Vendor Name set to 'BOA CC'</t>
+          <t>Vendor Name auto-set to 'BOA CC'</t>
         </is>
       </c>
     </row>
     <row r="223" ht="16" customHeight="1">
-      <c r="B223" s="58" t="inlineStr">
+      <c r="B223" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="C223" s="58" t="inlineStr">
+      <c r="C223" s="71" t="inlineStr">
         <is>
           <t>07/26/2026</t>
         </is>
       </c>
-      <c r="D223" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E223" s="58" t="inlineStr"/>
-      <c r="F223" s="58" t="inlineStr"/>
-      <c r="G223" s="58" t="inlineStr">
+      <c r="D223" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E223" s="71" t="inlineStr"/>
+      <c r="F223" s="71" t="inlineStr"/>
+      <c r="G223" s="71" t="inlineStr">
         <is>
           <t>CLUB 28 BADMINTON DELE 9176316713 DE</t>
         </is>
       </c>
-      <c r="H223" s="58" t="inlineStr">
+      <c r="H223" s="71" t="inlineStr">
         <is>
           <t>Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
-      <c r="I223" s="59" t="n">
+      <c r="I223" s="72" t="n">
         <v>140</v>
       </c>
-      <c r="J223" s="59" t="n">
+      <c r="J223" s="72" t="n">
         <v>647.9900000000002</v>
       </c>
-      <c r="K223" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L223" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K223" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L223" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Owners Distribution' based on historical data, found 'Meals &amp; Entertainment:Meals with clients'.</t>
         </is>
       </c>
     </row>
@@ -12292,7 +11672,7 @@
       </c>
       <c r="L224" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Meals &amp; Entertainment:Meals with clients', found 'Meals &amp; Entertainment:Entertainment'.</t>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Meals &amp; Entertainment:Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -12337,7 +11717,7 @@
       </c>
       <c r="L225" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Meals &amp; Entertainment:Meals with clients', found 'Meals &amp; Entertainment:Entertainment'.</t>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Meals &amp; Entertainment:Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -12410,7 +11790,7 @@
       </c>
       <c r="L229" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: 401K Payable</t>
+          <t>Verified: 401K Payable</t>
         </is>
       </c>
     </row>
@@ -12492,7 +11872,7 @@
       </c>
       <c r="L231" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: 401K Payable</t>
+          <t>Verified: 401K Payable</t>
         </is>
       </c>
     </row>
@@ -12617,7 +11997,7 @@
       </c>
       <c r="L238" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll wages and tax to pay:Payroll tax to pay</t>
+          <t>Verified: Payroll tax to pay</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12079,7 @@
       </c>
       <c r="L240" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll wages and tax to pay:Payroll tax to pay</t>
+          <t>Verified: Payroll tax to pay</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12165,7 @@
       </c>
       <c r="L242" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll wages and tax to pay:Payroll tax to pay</t>
+          <t>Verified: Payroll tax to pay</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12286,7 @@
       </c>
       <c r="L248" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Payroll Wages Payable</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12368,7 @@
       </c>
       <c r="L250" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Payroll Wages Payable</t>
         </is>
       </c>
     </row>
@@ -13074,7 +12454,7 @@
       </c>
       <c r="L252" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Payroll Wages Payable</t>
         </is>
       </c>
     </row>
@@ -13212,7 +12592,7 @@
       </c>
       <c r="L260" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -13257,7 +12637,7 @@
       </c>
       <c r="L261" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -13302,7 +12682,7 @@
       </c>
       <c r="L262" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -13347,7 +12727,7 @@
       </c>
       <c r="L263" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Verified: Shareholders' equity:Distributions</t>
         </is>
       </c>
     </row>
@@ -13392,7 +12772,7 @@
       </c>
       <c r="L264" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Owners Distribution</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -13500,7 +12880,7 @@
       </c>
       <c r="L272" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Shareholders' equity:Distributions</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -13544,1221 +12924,1221 @@
       </c>
     </row>
     <row r="277" ht="16" customHeight="1">
-      <c r="B277" s="71" t="inlineStr">
+      <c r="B277" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C277" s="71" t="inlineStr">
+      <c r="C277" s="58" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="D277" s="71" t="inlineStr">
+      <c r="D277" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E277" s="71" t="inlineStr">
+      <c r="E277" s="58" t="inlineStr">
         <is>
           <t>1546</t>
         </is>
       </c>
-      <c r="F277" s="71" t="inlineStr">
+      <c r="F277" s="58" t="inlineStr">
         <is>
           <t>Medix Staffing Solutions, LLC,</t>
         </is>
       </c>
-      <c r="G277" s="71" t="inlineStr">
+      <c r="G277" s="58" t="inlineStr">
         <is>
           <t>Back-End Power BI Developer - 07/01/26 - 07/05/26</t>
         </is>
       </c>
-      <c r="H277" s="71" t="inlineStr">
+      <c r="H277" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I277" s="72" t="n">
+      <c r="I277" s="59" t="n">
         <v>1336</v>
       </c>
-      <c r="J277" s="72" t="n">
+      <c r="J277" s="59" t="n">
         <v>1065127.51</v>
       </c>
-      <c r="K277" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L277" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K277" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L277" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="278" ht="16" customHeight="1">
-      <c r="B278" s="71" t="inlineStr">
+      <c r="B278" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C278" s="71" t="inlineStr">
+      <c r="C278" s="58" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="D278" s="71" t="inlineStr">
+      <c r="D278" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E278" s="71" t="inlineStr">
+      <c r="E278" s="58" t="inlineStr">
         <is>
           <t>1546</t>
         </is>
       </c>
-      <c r="F278" s="71" t="inlineStr">
+      <c r="F278" s="58" t="inlineStr">
         <is>
           <t>Medix Staffing Solutions, LLC,</t>
         </is>
       </c>
-      <c r="G278" s="71" t="inlineStr">
+      <c r="G278" s="58" t="inlineStr">
         <is>
           <t>Back-End Power BI Developer - 07/06/26 - 07/12/26</t>
         </is>
       </c>
-      <c r="H278" s="71" t="inlineStr">
+      <c r="H278" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I278" s="72" t="n">
+      <c r="I278" s="59" t="n">
         <v>3340</v>
       </c>
-      <c r="J278" s="72" t="n">
+      <c r="J278" s="59" t="n">
         <v>1068467.51</v>
       </c>
-      <c r="K278" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L278" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K278" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L278" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="279" ht="16" customHeight="1">
-      <c r="B279" s="71" t="inlineStr">
+      <c r="B279" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C279" s="71" t="inlineStr">
+      <c r="C279" s="58" t="inlineStr">
         <is>
           <t>07/20/2026</t>
         </is>
       </c>
-      <c r="D279" s="71" t="inlineStr">
+      <c r="D279" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E279" s="71" t="inlineStr">
+      <c r="E279" s="58" t="inlineStr">
         <is>
           <t>1555</t>
         </is>
       </c>
-      <c r="F279" s="71" t="inlineStr">
+      <c r="F279" s="58" t="inlineStr">
         <is>
           <t>Medix Staffing Solutions, LLC,</t>
         </is>
       </c>
-      <c r="G279" s="71" t="inlineStr">
+      <c r="G279" s="58" t="inlineStr">
         <is>
           <t>Back-End Power BI Developer - 07/13/26 - 07/19/26</t>
         </is>
       </c>
-      <c r="H279" s="71" t="inlineStr">
+      <c r="H279" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I279" s="72" t="n">
+      <c r="I279" s="59" t="n">
         <v>3340</v>
       </c>
-      <c r="J279" s="72" t="n">
+      <c r="J279" s="59" t="n">
         <v>1071807.51</v>
       </c>
-      <c r="K279" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L279" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K279" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L279" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="280" ht="16" customHeight="1">
-      <c r="B280" s="71" t="inlineStr">
+      <c r="B280" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C280" s="71" t="inlineStr">
+      <c r="C280" s="58" t="inlineStr">
         <is>
           <t>07/20/2026</t>
         </is>
       </c>
-      <c r="D280" s="71" t="inlineStr">
+      <c r="D280" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E280" s="71" t="inlineStr">
+      <c r="E280" s="58" t="inlineStr">
         <is>
           <t>1555</t>
         </is>
       </c>
-      <c r="F280" s="71" t="inlineStr">
+      <c r="F280" s="58" t="inlineStr">
         <is>
           <t>Medix Staffing Solutions, LLC,</t>
         </is>
       </c>
-      <c r="G280" s="71" t="inlineStr">
+      <c r="G280" s="58" t="inlineStr">
         <is>
           <t>Back-End Power BI Developer - 07/19/26 - 07/25/26</t>
         </is>
       </c>
-      <c r="H280" s="71" t="inlineStr">
+      <c r="H280" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I280" s="72" t="n">
+      <c r="I280" s="59" t="n">
         <v>3340</v>
       </c>
-      <c r="J280" s="72" t="n">
+      <c r="J280" s="59" t="n">
         <v>1075147.51</v>
       </c>
-      <c r="K280" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L280" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K280" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L280" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="281" ht="16" customHeight="1">
-      <c r="B281" s="71" t="inlineStr">
+      <c r="B281" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C281" s="71" t="inlineStr">
+      <c r="C281" s="58" t="inlineStr">
         <is>
           <t>07/20/2026</t>
         </is>
       </c>
-      <c r="D281" s="71" t="inlineStr">
+      <c r="D281" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E281" s="71" t="inlineStr">
+      <c r="E281" s="58" t="inlineStr">
         <is>
           <t>1555</t>
         </is>
       </c>
-      <c r="F281" s="71" t="inlineStr">
+      <c r="F281" s="58" t="inlineStr">
         <is>
           <t>Medix Staffing Solutions, LLC,</t>
         </is>
       </c>
-      <c r="G281" s="71" t="inlineStr">
+      <c r="G281" s="58" t="inlineStr">
         <is>
           <t>Back-End Power BI Developer - 07/26/26 - 07/31/26</t>
         </is>
       </c>
-      <c r="H281" s="71" t="inlineStr">
+      <c r="H281" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I281" s="72" t="n">
+      <c r="I281" s="59" t="n">
         <v>3340</v>
       </c>
-      <c r="J281" s="72" t="n">
+      <c r="J281" s="59" t="n">
         <v>1078487.51</v>
       </c>
-      <c r="K281" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L281" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K281" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L281" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="282" ht="16" customHeight="1">
-      <c r="B282" s="71" t="inlineStr">
+      <c r="B282" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C282" s="71" t="inlineStr">
+      <c r="C282" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D282" s="71" t="inlineStr">
+      <c r="D282" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E282" s="71" t="inlineStr">
+      <c r="E282" s="58" t="inlineStr">
         <is>
           <t>1538</t>
         </is>
       </c>
-      <c r="F282" s="71" t="inlineStr">
+      <c r="F282" s="58" t="inlineStr">
         <is>
           <t>Phoenix Staff Inc</t>
         </is>
       </c>
-      <c r="G282" s="71" t="inlineStr">
+      <c r="G282" s="58" t="inlineStr">
         <is>
           <t>07/01/26 - 07/05/26</t>
         </is>
       </c>
-      <c r="H282" s="71" t="inlineStr">
+      <c r="H282" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I282" s="72" t="n">
+      <c r="I282" s="59" t="n">
         <v>1104</v>
       </c>
-      <c r="J282" s="72" t="n">
+      <c r="J282" s="59" t="n">
         <v>1079591.51</v>
       </c>
-      <c r="K282" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L282" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K282" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L282" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="283" ht="16" customHeight="1">
-      <c r="B283" s="71" t="inlineStr">
+      <c r="B283" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C283" s="71" t="inlineStr">
+      <c r="C283" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D283" s="71" t="inlineStr">
+      <c r="D283" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E283" s="71" t="inlineStr">
+      <c r="E283" s="58" t="inlineStr">
         <is>
           <t>1538</t>
         </is>
       </c>
-      <c r="F283" s="71" t="inlineStr">
+      <c r="F283" s="58" t="inlineStr">
         <is>
           <t>Phoenix Staff Inc</t>
         </is>
       </c>
-      <c r="G283" s="71" t="inlineStr">
+      <c r="G283" s="58" t="inlineStr">
         <is>
           <t>07/06/26 - 07/12/26</t>
         </is>
       </c>
-      <c r="H283" s="71" t="inlineStr">
+      <c r="H283" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I283" s="72" t="n">
+      <c r="I283" s="59" t="n">
         <v>2760</v>
       </c>
-      <c r="J283" s="72" t="n">
+      <c r="J283" s="59" t="n">
         <v>1082351.51</v>
       </c>
-      <c r="K283" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L283" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K283" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L283" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="284" ht="16" customHeight="1">
-      <c r="B284" s="71" t="inlineStr">
+      <c r="B284" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C284" s="71" t="inlineStr">
+      <c r="C284" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D284" s="71" t="inlineStr">
+      <c r="D284" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E284" s="71" t="inlineStr">
+      <c r="E284" s="58" t="inlineStr">
         <is>
           <t>1538</t>
         </is>
       </c>
-      <c r="F284" s="71" t="inlineStr">
+      <c r="F284" s="58" t="inlineStr">
         <is>
           <t>Phoenix Staff Inc</t>
         </is>
       </c>
-      <c r="G284" s="71" t="inlineStr">
+      <c r="G284" s="58" t="inlineStr">
         <is>
           <t>07/13/26 - 07/19/26</t>
         </is>
       </c>
-      <c r="H284" s="71" t="inlineStr">
+      <c r="H284" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I284" s="72" t="n">
+      <c r="I284" s="59" t="n">
         <v>2760</v>
       </c>
-      <c r="J284" s="72" t="n">
+      <c r="J284" s="59" t="n">
         <v>1085111.51</v>
       </c>
-      <c r="K284" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L284" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K284" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L284" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="285" ht="16" customHeight="1">
-      <c r="B285" s="71" t="inlineStr">
+      <c r="B285" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C285" s="71" t="inlineStr">
+      <c r="C285" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D285" s="71" t="inlineStr">
+      <c r="D285" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E285" s="71" t="inlineStr">
+      <c r="E285" s="58" t="inlineStr">
         <is>
           <t>1538</t>
         </is>
       </c>
-      <c r="F285" s="71" t="inlineStr">
+      <c r="F285" s="58" t="inlineStr">
         <is>
           <t>Phoenix Staff Inc</t>
         </is>
       </c>
-      <c r="G285" s="71" t="inlineStr">
+      <c r="G285" s="58" t="inlineStr">
         <is>
           <t>07/20/26 - 07/26/26</t>
         </is>
       </c>
-      <c r="H285" s="71" t="inlineStr">
+      <c r="H285" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I285" s="72" t="n">
+      <c r="I285" s="59" t="n">
         <v>2600</v>
       </c>
-      <c r="J285" s="72" t="n">
+      <c r="J285" s="59" t="n">
         <v>1087711.51</v>
       </c>
-      <c r="K285" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L285" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K285" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L285" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="286" ht="16" customHeight="1">
-      <c r="B286" s="71" t="inlineStr">
+      <c r="B286" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C286" s="71" t="inlineStr">
+      <c r="C286" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D286" s="71" t="inlineStr">
+      <c r="D286" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E286" s="71" t="inlineStr">
+      <c r="E286" s="58" t="inlineStr">
         <is>
           <t>1538</t>
         </is>
       </c>
-      <c r="F286" s="71" t="inlineStr">
+      <c r="F286" s="58" t="inlineStr">
         <is>
           <t>Phoenix Staff Inc</t>
         </is>
       </c>
-      <c r="G286" s="71" t="inlineStr">
+      <c r="G286" s="58" t="inlineStr">
         <is>
           <t>07/27/26 - 07/31/26</t>
         </is>
       </c>
-      <c r="H286" s="71" t="inlineStr">
+      <c r="H286" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I286" s="72" t="n">
+      <c r="I286" s="59" t="n">
         <v>2600</v>
       </c>
-      <c r="J286" s="72" t="n">
+      <c r="J286" s="59" t="n">
         <v>1090311.51</v>
       </c>
-      <c r="K286" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L286" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K286" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L286" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="287" ht="16" customHeight="1">
-      <c r="B287" s="71" t="inlineStr">
+      <c r="B287" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C287" s="71" t="inlineStr">
+      <c r="C287" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D287" s="71" t="inlineStr">
+      <c r="D287" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E287" s="71" t="inlineStr">
+      <c r="E287" s="58" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="F287" s="71" t="inlineStr">
+      <c r="F287" s="58" t="inlineStr">
         <is>
           <t>SANA Software Solutions</t>
         </is>
       </c>
-      <c r="G287" s="71" t="inlineStr">
+      <c r="G287" s="58" t="inlineStr">
         <is>
           <t>Nithya Tejasvini Baddam - July 2026</t>
         </is>
       </c>
-      <c r="H287" s="71" t="inlineStr">
+      <c r="H287" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I287" s="72" t="n">
+      <c r="I287" s="59" t="n">
         <v>11440</v>
       </c>
-      <c r="J287" s="72" t="n">
+      <c r="J287" s="59" t="n">
         <v>1101751.51</v>
       </c>
-      <c r="K287" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L287" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K287" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L287" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="288" ht="16" customHeight="1">
-      <c r="B288" s="71" t="inlineStr">
+      <c r="B288" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C288" s="71" t="inlineStr">
+      <c r="C288" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D288" s="71" t="inlineStr">
+      <c r="D288" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E288" s="71" t="inlineStr">
+      <c r="E288" s="58" t="inlineStr">
         <is>
           <t>1601</t>
         </is>
       </c>
-      <c r="F288" s="71" t="inlineStr">
+      <c r="F288" s="58" t="inlineStr">
         <is>
           <t>Nityo Infotech Corporation</t>
         </is>
       </c>
-      <c r="G288" s="71" t="inlineStr">
+      <c r="G288" s="58" t="inlineStr">
         <is>
           <t>07/01/26 - 07/31/26</t>
         </is>
       </c>
-      <c r="H288" s="71" t="inlineStr">
+      <c r="H288" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I288" s="72" t="n">
+      <c r="I288" s="59" t="n">
         <v>13024</v>
       </c>
-      <c r="J288" s="72" t="n">
+      <c r="J288" s="59" t="n">
         <v>1114775.51</v>
       </c>
-      <c r="K288" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L288" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K288" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L288" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="289" ht="16" customHeight="1">
-      <c r="B289" s="71" t="inlineStr">
+      <c r="B289" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C289" s="71" t="inlineStr">
+      <c r="C289" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D289" s="71" t="inlineStr">
+      <c r="D289" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E289" s="71" t="inlineStr">
+      <c r="E289" s="58" t="inlineStr">
         <is>
           <t>1601</t>
         </is>
       </c>
-      <c r="F289" s="71" t="inlineStr">
+      <c r="F289" s="58" t="inlineStr">
         <is>
           <t>Nityo Infotech Corporation</t>
         </is>
       </c>
-      <c r="G289" s="71" t="inlineStr">
+      <c r="G289" s="58" t="inlineStr">
         <is>
           <t>1.2% payment fee for Vendor Management Charges</t>
         </is>
       </c>
-      <c r="H289" s="71" t="inlineStr">
+      <c r="H289" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I289" s="72" t="n">
+      <c r="I289" s="59" t="n">
         <v>-156.28</v>
       </c>
-      <c r="J289" s="72" t="n">
+      <c r="J289" s="59" t="n">
         <v>1114619.23</v>
       </c>
-      <c r="K289" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L289" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K289" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L289" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="290" ht="16" customHeight="1">
-      <c r="B290" s="71" t="inlineStr">
+      <c r="B290" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C290" s="71" t="inlineStr">
+      <c r="C290" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D290" s="71" t="inlineStr">
+      <c r="D290" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E290" s="71" t="inlineStr">
+      <c r="E290" s="58" t="inlineStr">
         <is>
           <t>1602</t>
         </is>
       </c>
-      <c r="F290" s="71" t="inlineStr">
+      <c r="F290" s="58" t="inlineStr">
         <is>
           <t>Vivid Technologies Inc</t>
         </is>
       </c>
-      <c r="G290" s="71" t="inlineStr">
+      <c r="G290" s="58" t="inlineStr">
         <is>
           <t>Professional Services from the period 07/01/26 - 07/31/26</t>
         </is>
       </c>
-      <c r="H290" s="71" t="inlineStr">
+      <c r="H290" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I290" s="72" t="n">
+      <c r="I290" s="59" t="n">
         <v>10920</v>
       </c>
-      <c r="J290" s="72" t="n">
+      <c r="J290" s="59" t="n">
         <v>1125539.23</v>
       </c>
-      <c r="K290" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L290" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K290" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L290" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="291" ht="16" customHeight="1">
-      <c r="B291" s="71" t="inlineStr">
+      <c r="B291" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C291" s="71" t="inlineStr">
+      <c r="C291" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D291" s="71" t="inlineStr">
+      <c r="D291" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E291" s="71" t="inlineStr">
+      <c r="E291" s="58" t="inlineStr">
         <is>
           <t>1604</t>
         </is>
       </c>
-      <c r="F291" s="71" t="inlineStr">
+      <c r="F291" s="58" t="inlineStr">
         <is>
           <t>Bigbyte</t>
         </is>
       </c>
-      <c r="G291" s="71" t="inlineStr">
+      <c r="G291" s="58" t="inlineStr">
         <is>
           <t>Professional Services from the period 07/01/26 -07/31/26</t>
         </is>
       </c>
-      <c r="H291" s="71" t="inlineStr">
+      <c r="H291" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I291" s="72" t="n">
+      <c r="I291" s="59" t="n">
         <v>11792</v>
       </c>
-      <c r="J291" s="72" t="n">
+      <c r="J291" s="59" t="n">
         <v>1137331.23</v>
       </c>
-      <c r="K291" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L291" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K291" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L291" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="292" ht="16" customHeight="1">
-      <c r="B292" s="71" t="inlineStr">
+      <c r="B292" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C292" s="71" t="inlineStr">
+      <c r="C292" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D292" s="71" t="inlineStr">
+      <c r="D292" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E292" s="71" t="inlineStr">
+      <c r="E292" s="58" t="inlineStr">
         <is>
           <t>1603</t>
         </is>
       </c>
-      <c r="F292" s="71" t="inlineStr">
+      <c r="F292" s="58" t="inlineStr">
         <is>
           <t>Randstand Digital</t>
         </is>
       </c>
-      <c r="G292" s="71" t="inlineStr">
+      <c r="G292" s="58" t="inlineStr">
         <is>
           <t>Venkata Vinay Kumar 07/01/2026 -07/31/2026</t>
         </is>
       </c>
-      <c r="H292" s="71" t="inlineStr">
+      <c r="H292" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I292" s="72" t="n">
+      <c r="I292" s="59" t="n">
         <v>7136.8</v>
       </c>
-      <c r="J292" s="72" t="n">
+      <c r="J292" s="59" t="n">
         <v>1144468.03</v>
       </c>
-      <c r="K292" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L292" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K292" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L292" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="293" ht="16" customHeight="1">
-      <c r="B293" s="71" t="inlineStr">
+      <c r="B293" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C293" s="71" t="inlineStr">
+      <c r="C293" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D293" s="71" t="inlineStr">
+      <c r="D293" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E293" s="71" t="inlineStr">
+      <c r="E293" s="58" t="inlineStr">
         <is>
           <t>1605</t>
         </is>
       </c>
-      <c r="F293" s="71" t="inlineStr">
+      <c r="F293" s="58" t="inlineStr">
         <is>
           <t>AGILISIUM CONSULTING LLC</t>
         </is>
       </c>
-      <c r="G293" s="71" t="inlineStr">
+      <c r="G293" s="58" t="inlineStr">
         <is>
           <t>Gadupudi Ravi Kumar – Professional Services for the period 07/01/26 - 07/31/26</t>
         </is>
       </c>
-      <c r="H293" s="71" t="inlineStr">
+      <c r="H293" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I293" s="72" t="n">
+      <c r="I293" s="59" t="n">
         <v>4048</v>
       </c>
-      <c r="J293" s="72" t="n">
+      <c r="J293" s="59" t="n">
         <v>1148516.03</v>
       </c>
-      <c r="K293" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L293" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K293" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L293" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="294" ht="16" customHeight="1">
-      <c r="B294" s="71" t="inlineStr">
+      <c r="B294" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C294" s="71" t="inlineStr">
+      <c r="C294" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D294" s="71" t="inlineStr">
+      <c r="D294" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E294" s="71" t="inlineStr">
+      <c r="E294" s="58" t="inlineStr">
         <is>
           <t>1606</t>
         </is>
       </c>
-      <c r="F294" s="71" t="inlineStr">
+      <c r="F294" s="58" t="inlineStr">
         <is>
           <t>Infinite Computer Solutions Inc.</t>
         </is>
       </c>
-      <c r="G294" s="71" t="inlineStr">
+      <c r="G294" s="58" t="inlineStr">
         <is>
           <t>07/01/26 - 07/31/26 (Invoice I- 496082)</t>
         </is>
       </c>
-      <c r="H294" s="71" t="inlineStr">
+      <c r="H294" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I294" s="72" t="n">
+      <c r="I294" s="59" t="n">
         <v>12414.48</v>
       </c>
-      <c r="J294" s="72" t="n">
+      <c r="J294" s="59" t="n">
         <v>1160930.51</v>
       </c>
-      <c r="K294" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L294" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K294" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L294" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="295" ht="16" customHeight="1">
-      <c r="B295" s="71" t="inlineStr">
+      <c r="B295" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C295" s="71" t="inlineStr">
+      <c r="C295" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D295" s="71" t="inlineStr">
+      <c r="D295" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E295" s="71" t="inlineStr">
+      <c r="E295" s="58" t="inlineStr">
         <is>
           <t>1607</t>
         </is>
       </c>
-      <c r="F295" s="71" t="inlineStr">
+      <c r="F295" s="58" t="inlineStr">
         <is>
           <t>American Technology Services LLC</t>
         </is>
       </c>
-      <c r="G295" s="71" t="inlineStr">
+      <c r="G295" s="58" t="inlineStr">
         <is>
           <t>Nagendra Jaggarapu - 07/01/26 - 07/31/26 (Work Order# OMF-CW-0003240)</t>
         </is>
       </c>
-      <c r="H295" s="71" t="inlineStr">
+      <c r="H295" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I295" s="72" t="n">
+      <c r="I295" s="59" t="n">
         <v>16800</v>
       </c>
-      <c r="J295" s="72" t="n">
+      <c r="J295" s="59" t="n">
         <v>1177730.51</v>
       </c>
-      <c r="K295" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L295" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K295" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L295" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="296" ht="16" customHeight="1">
-      <c r="B296" s="71" t="inlineStr">
+      <c r="B296" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C296" s="71" t="inlineStr">
+      <c r="C296" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D296" s="71" t="inlineStr">
+      <c r="D296" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E296" s="71" t="inlineStr">
+      <c r="E296" s="58" t="inlineStr">
         <is>
           <t>1608</t>
         </is>
       </c>
-      <c r="F296" s="71" t="inlineStr">
+      <c r="F296" s="58" t="inlineStr">
         <is>
           <t>Sage Solutions LLC</t>
         </is>
       </c>
-      <c r="G296" s="71" t="inlineStr">
+      <c r="G296" s="58" t="inlineStr">
         <is>
           <t>Sravan Tadepalli_07/01/26- 07/31/26</t>
         </is>
       </c>
-      <c r="H296" s="71" t="inlineStr">
+      <c r="H296" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I296" s="72" t="n">
+      <c r="I296" s="59" t="n">
         <v>11264</v>
       </c>
-      <c r="J296" s="72" t="n">
+      <c r="J296" s="59" t="n">
         <v>1188994.51</v>
       </c>
-      <c r="K296" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L296" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Consulting Fees', found 'Services'.</t>
+      <c r="K296" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L296" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="297" ht="16" customHeight="1">
-      <c r="B297" s="71" t="inlineStr">
+      <c r="B297" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C297" s="71" t="inlineStr">
+      <c r="C297" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D297" s="71" t="inlineStr">
+      <c r="D297" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E297" s="71" t="inlineStr">
+      <c r="E297" s="58" t="inlineStr">
         <is>
           <t>1609</t>
         </is>
       </c>
-      <c r="F297" s="71" t="inlineStr">
+      <c r="F297" s="58" t="inlineStr">
         <is>
           <t>American Technology Services LLC</t>
         </is>
       </c>
-      <c r="G297" s="71" t="inlineStr">
+      <c r="G297" s="58" t="inlineStr">
         <is>
           <t>Professional Services from the period 07/01/26 - 07/31/26 (Work Order# OMF-WO-0003012)</t>
         </is>
       </c>
-      <c r="H297" s="71" t="inlineStr">
+      <c r="H297" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I297" s="72" t="n">
+      <c r="I297" s="59" t="n">
         <v>11440</v>
       </c>
-      <c r="J297" s="72" t="n">
+      <c r="J297" s="59" t="n">
         <v>1200434.51</v>
       </c>
-      <c r="K297" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L297" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K297" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L297" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="298" ht="16" customHeight="1">
-      <c r="B298" s="71" t="inlineStr">
+      <c r="B298" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C298" s="71" t="inlineStr">
+      <c r="C298" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D298" s="71" t="inlineStr">
+      <c r="D298" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E298" s="71" t="inlineStr">
+      <c r="E298" s="58" t="inlineStr">
         <is>
           <t>1615</t>
         </is>
       </c>
-      <c r="F298" s="71" t="inlineStr">
+      <c r="F298" s="58" t="inlineStr">
         <is>
           <t>AGILISIUM CONSULTING LLC</t>
         </is>
       </c>
-      <c r="G298" s="71" t="inlineStr">
+      <c r="G298" s="58" t="inlineStr">
         <is>
           <t>Rakesh Varma Uppalapati _ 07/01/26 - 07/31/26</t>
         </is>
       </c>
-      <c r="H298" s="71" t="inlineStr">
+      <c r="H298" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I298" s="72" t="n">
+      <c r="I298" s="59" t="n">
         <v>14960</v>
       </c>
-      <c r="J298" s="72" t="n">
+      <c r="J298" s="59" t="n">
         <v>1215394.51</v>
       </c>
-      <c r="K298" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L298" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K298" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L298" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
     <row r="299" ht="16" customHeight="1">
-      <c r="B299" s="71" t="inlineStr">
+      <c r="B299" s="58" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C299" s="71" t="inlineStr">
+      <c r="C299" s="58" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D299" s="71" t="inlineStr">
+      <c r="D299" s="58" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E299" s="71" t="inlineStr">
+      <c r="E299" s="58" t="inlineStr">
         <is>
           <t>1618</t>
         </is>
       </c>
-      <c r="F299" s="71" t="inlineStr">
+      <c r="F299" s="58" t="inlineStr">
         <is>
           <t>Vendorpass, INC</t>
         </is>
       </c>
-      <c r="G299" s="71" t="inlineStr">
+      <c r="G299" s="58" t="inlineStr">
         <is>
           <t>07/01/26-07/31/26</t>
         </is>
       </c>
-      <c r="H299" s="71" t="inlineStr">
+      <c r="H299" s="58" t="inlineStr">
         <is>
           <t>Accounts Receivable (A/R)</t>
         </is>
       </c>
-      <c r="I299" s="72" t="n">
+      <c r="I299" s="59" t="n">
         <v>9328</v>
       </c>
-      <c r="J299" s="72" t="n">
+      <c r="J299" s="59" t="n">
         <v>1224722.51</v>
       </c>
-      <c r="K299" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L299" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Receivable (A/R)', found 'Services'.</t>
+      <c r="K299" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L299" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Receivable (A/R)</t>
         </is>
       </c>
     </row>
@@ -14854,210 +14234,210 @@
       </c>
     </row>
     <row r="306" ht="16" customHeight="1">
-      <c r="B306" s="71" t="inlineStr">
+      <c r="B306" s="58" t="inlineStr">
         <is>
           <t>COGS - Vendor</t>
         </is>
       </c>
-      <c r="C306" s="71" t="inlineStr">
+      <c r="C306" s="58" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="D306" s="71" t="inlineStr">
+      <c r="D306" s="58" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E306" s="71" t="inlineStr">
+      <c r="E306" s="58" t="inlineStr">
         <is>
           <t>ASM044</t>
         </is>
       </c>
-      <c r="F306" s="71" t="inlineStr">
+      <c r="F306" s="58" t="inlineStr">
         <is>
           <t>Astramind Solutions Private Limited</t>
         </is>
       </c>
-      <c r="G306" s="71" t="inlineStr">
+      <c r="G306" s="58" t="inlineStr">
         <is>
           <t>Offshore IT Support Services - June 2026</t>
         </is>
       </c>
-      <c r="H306" s="71" t="inlineStr">
+      <c r="H306" s="58" t="inlineStr">
         <is>
           <t>Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I306" s="72" t="n">
+      <c r="I306" s="59" t="n">
         <v>12675.9</v>
       </c>
-      <c r="J306" s="72" t="n">
+      <c r="J306" s="59" t="n">
         <v>216547.32</v>
       </c>
-      <c r="K306" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L306" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Payable (A/P)', found 'COGS - Vendor'.</t>
+      <c r="K306" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L306" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
     <row r="307" ht="16" customHeight="1">
-      <c r="B307" s="71" t="inlineStr">
+      <c r="B307" s="58" t="inlineStr">
         <is>
           <t>COGS - Vendor</t>
         </is>
       </c>
-      <c r="C307" s="71" t="inlineStr">
+      <c r="C307" s="58" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D307" s="71" t="inlineStr">
+      <c r="D307" s="58" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E307" s="71" t="inlineStr">
+      <c r="E307" s="58" t="inlineStr">
         <is>
           <t>ASM045</t>
         </is>
       </c>
-      <c r="F307" s="71" t="inlineStr">
+      <c r="F307" s="58" t="inlineStr">
         <is>
           <t>Astramind Solutions Private Limited</t>
         </is>
       </c>
-      <c r="G307" s="71" t="inlineStr">
+      <c r="G307" s="58" t="inlineStr">
         <is>
           <t>Offshore marketing and web development services - ₹9,02,720.00</t>
         </is>
       </c>
-      <c r="H307" s="71" t="inlineStr">
+      <c r="H307" s="58" t="inlineStr">
         <is>
           <t>Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I307" s="72" t="n">
+      <c r="I307" s="59" t="n">
         <v>9541.690000000001</v>
       </c>
-      <c r="J307" s="72" t="n">
+      <c r="J307" s="59" t="n">
         <v>226089.01</v>
       </c>
-      <c r="K307" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L307" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Payable (A/P)', found 'COGS - Vendor'.</t>
+      <c r="K307" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L307" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
     <row r="308" ht="16" customHeight="1">
-      <c r="B308" s="71" t="inlineStr">
+      <c r="B308" s="58" t="inlineStr">
         <is>
           <t>COGS - Vendor</t>
         </is>
       </c>
-      <c r="C308" s="71" t="inlineStr">
+      <c r="C308" s="58" t="inlineStr">
         <is>
           <t>07/22/2026</t>
         </is>
       </c>
-      <c r="D308" s="71" t="inlineStr">
+      <c r="D308" s="58" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E308" s="71" t="inlineStr">
+      <c r="E308" s="58" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F308" s="71" t="inlineStr">
+      <c r="F308" s="58" t="inlineStr">
         <is>
           <t>Aneru LLC</t>
         </is>
       </c>
-      <c r="G308" s="71" t="inlineStr"/>
-      <c r="H308" s="71" t="inlineStr">
+      <c r="G308" s="58" t="inlineStr"/>
+      <c r="H308" s="58" t="inlineStr">
         <is>
           <t>Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I308" s="72" t="n">
+      <c r="I308" s="59" t="n">
         <v>15556</v>
       </c>
-      <c r="J308" s="72" t="n">
+      <c r="J308" s="59" t="n">
         <v>241645.01</v>
       </c>
-      <c r="K308" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L308" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Payable (A/P)', found 'COGS - Vendor'.</t>
+      <c r="K308" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L308" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
     <row r="309" ht="16" customHeight="1">
-      <c r="B309" s="71" t="inlineStr">
+      <c r="B309" s="58" t="inlineStr">
         <is>
           <t>COGS - Vendor</t>
         </is>
       </c>
-      <c r="C309" s="71" t="inlineStr">
+      <c r="C309" s="58" t="inlineStr">
         <is>
           <t>07/28/2026</t>
         </is>
       </c>
-      <c r="D309" s="71" t="inlineStr">
+      <c r="D309" s="58" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E309" s="71" t="inlineStr">
+      <c r="E309" s="58" t="inlineStr">
         <is>
           <t>VSL07282026</t>
         </is>
       </c>
-      <c r="F309" s="71" t="inlineStr">
+      <c r="F309" s="58" t="inlineStr">
         <is>
           <t>PTL Consultancy</t>
         </is>
       </c>
-      <c r="G309" s="71" t="inlineStr">
+      <c r="G309" s="58" t="inlineStr">
         <is>
           <t>India July 2026 Salaries -  SUBTOTAL INR 528,875.00</t>
         </is>
       </c>
-      <c r="H309" s="71" t="inlineStr">
+      <c r="H309" s="58" t="inlineStr">
         <is>
           <t>Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I309" s="72" t="n">
+      <c r="I309" s="59" t="n">
         <v>5546.55</v>
       </c>
-      <c r="J309" s="72" t="n">
+      <c r="J309" s="59" t="n">
         <v>247191.56</v>
       </c>
-      <c r="K309" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L309" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Accounts Payable (A/P)', found 'COGS - Vendor'.</t>
+      <c r="K309" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L309" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
@@ -15288,60 +14668,60 @@
       </c>
       <c r="L320" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Consulting Fees</t>
+          <t>Verified: Accounts Payable (A/P)</t>
         </is>
       </c>
     </row>
     <row r="321" ht="16" customHeight="1">
-      <c r="B321" s="58" t="inlineStr">
+      <c r="B321" s="71" t="inlineStr">
         <is>
           <t>Consulting Fees</t>
         </is>
       </c>
-      <c r="C321" s="58" t="inlineStr">
+      <c r="C321" s="71" t="inlineStr">
         <is>
           <t>07/31/2026</t>
         </is>
       </c>
-      <c r="D321" s="58" t="inlineStr">
+      <c r="D321" s="71" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E321" s="58" t="inlineStr">
+      <c r="E321" s="71" t="inlineStr">
         <is>
           <t>12282018626</t>
         </is>
       </c>
-      <c r="F321" s="58" t="inlineStr">
+      <c r="F321" s="71" t="inlineStr">
         <is>
           <t>Sage Solutions</t>
         </is>
       </c>
-      <c r="G321" s="58" t="inlineStr">
+      <c r="G321" s="71" t="inlineStr">
         <is>
           <t>Venkata Vinay Kumar 07/01/2026 -07/31/2026 (88*$77)</t>
         </is>
       </c>
-      <c r="H321" s="58" t="inlineStr">
+      <c r="H321" s="71" t="inlineStr">
         <is>
           <t>Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I321" s="59" t="n">
+      <c r="I321" s="72" t="n">
         <v>6776</v>
       </c>
-      <c r="J321" s="59" t="n">
+      <c r="J321" s="72" t="n">
         <v>179784</v>
       </c>
-      <c r="K321" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L321" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Consulting Fees</t>
+      <c r="K321" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L321" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Accounts Receivable (A/R)' based on historical data, found 'Consulting Fees'.</t>
         </is>
       </c>
     </row>
@@ -15442,52 +14822,52 @@
       </c>
       <c r="L328" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Dues &amp; subscriptions</t>
+          <t>Verified: Dues &amp; subscriptions</t>
         </is>
       </c>
     </row>
     <row r="329" ht="16" customHeight="1">
-      <c r="B329" s="71" t="inlineStr">
+      <c r="B329" s="58" t="inlineStr">
         <is>
           <t>Dues &amp; subscriptions</t>
         </is>
       </c>
-      <c r="C329" s="71" t="inlineStr">
+      <c r="C329" s="58" t="inlineStr">
         <is>
           <t>07/13/2026</t>
         </is>
       </c>
-      <c r="D329" s="71" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E329" s="71" t="inlineStr"/>
-      <c r="F329" s="71" t="inlineStr"/>
-      <c r="G329" s="71" t="inlineStr">
+      <c r="D329" s="58" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E329" s="58" t="inlineStr"/>
+      <c r="F329" s="58" t="inlineStr"/>
+      <c r="G329" s="58" t="inlineStr">
         <is>
           <t>OPENAI *CHATGPT SUBSCR 4158799686 CA</t>
         </is>
       </c>
-      <c r="H329" s="71" t="inlineStr">
+      <c r="H329" s="58" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I329" s="72" t="n">
+      <c r="I329" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="J329" s="72" t="n">
+      <c r="J329" s="59" t="n">
         <v>1363.14</v>
       </c>
-      <c r="K329" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L329" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Office expenses:Software &amp; apps', found 'Dues &amp; subscriptions'.</t>
+      <c r="K329" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L329" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Dues &amp; subscriptions</t>
         </is>
       </c>
     </row>
@@ -15612,7 +14992,7 @@
       </c>
       <c r="L335" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: General business expenses:Bank fees &amp; service charges</t>
         </is>
       </c>
     </row>
@@ -15685,7 +15065,7 @@
       </c>
       <c r="L339" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: General business expenses:Memberships &amp; subscriptions</t>
+          <t>Verified: General business expenses:Memberships &amp; subscriptions</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15110,7 @@
       </c>
       <c r="L340" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: General business expenses:Memberships &amp; subscriptions</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15155,7 @@
       </c>
       <c r="L341" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: General business expenses:Memberships &amp; subscriptions</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -15863,7 +15243,7 @@
       </c>
       <c r="L346" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Immigration Expenses</t>
+          <t>Verified: Immigration Expenses</t>
         </is>
       </c>
     </row>
@@ -15908,7 +15288,7 @@
       </c>
       <c r="L347" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Immigration Expenses</t>
+          <t>Verified: Immigration Expenses</t>
         </is>
       </c>
     </row>
@@ -15981,7 +15361,7 @@
       </c>
       <c r="L351" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Insurance</t>
+          <t>Verified: Insurance</t>
         </is>
       </c>
     </row>
@@ -16026,7 +15406,7 @@
       </c>
       <c r="L352" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Insurance</t>
+          <t>Verified: Insurance</t>
         </is>
       </c>
     </row>
@@ -16071,7 +15451,7 @@
       </c>
       <c r="L353" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Insurance</t>
+          <t>Verified: Insurance</t>
         </is>
       </c>
     </row>
@@ -16144,7 +15524,7 @@
       </c>
       <c r="L357" s="61" t="inlineStr">
         <is>
-          <t>Standard ledger entry</t>
+          <t>Verified: Interest paid</t>
         </is>
       </c>
     </row>
@@ -16229,47 +15609,47 @@
       </c>
     </row>
     <row r="363" ht="16" customHeight="1">
-      <c r="B363" s="58" t="inlineStr">
+      <c r="B363" s="71" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C363" s="58" t="inlineStr">
+      <c r="C363" s="71" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="D363" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E363" s="58" t="inlineStr"/>
-      <c r="F363" s="58" t="inlineStr"/>
-      <c r="G363" s="58" t="inlineStr">
+      <c r="D363" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E363" s="71" t="inlineStr"/>
+      <c r="F363" s="71" t="inlineStr"/>
+      <c r="G363" s="71" t="inlineStr">
         <is>
           <t>DD *DOORDASH HALALGYRO 8559731040 CA</t>
         </is>
       </c>
-      <c r="H363" s="58" t="inlineStr">
+      <c r="H363" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I363" s="59" t="n">
+      <c r="I363" s="72" t="n">
         <v>35.85</v>
       </c>
-      <c r="J363" s="59" t="n">
+      <c r="J363" s="72" t="n">
         <v>262.76</v>
       </c>
-      <c r="K363" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L363" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K363" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L363" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -16364,272 +15744,272 @@
       </c>
     </row>
     <row r="366" ht="16" customHeight="1">
-      <c r="B366" s="58" t="inlineStr">
+      <c r="B366" s="71" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C366" s="58" t="inlineStr">
+      <c r="C366" s="71" t="inlineStr">
         <is>
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="D366" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E366" s="58" t="inlineStr"/>
-      <c r="F366" s="58" t="inlineStr"/>
-      <c r="G366" s="58" t="inlineStr">
+      <c r="D366" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E366" s="71" t="inlineStr"/>
+      <c r="F366" s="71" t="inlineStr"/>
+      <c r="G366" s="71" t="inlineStr">
         <is>
           <t>DD *DOORDASH MASALAREP 8559731040 CA</t>
         </is>
       </c>
-      <c r="H366" s="58" t="inlineStr">
+      <c r="H366" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I366" s="59" t="n">
+      <c r="I366" s="72" t="n">
         <v>27.41</v>
       </c>
-      <c r="J366" s="59" t="n">
+      <c r="J366" s="72" t="n">
         <v>320.35</v>
       </c>
-      <c r="K366" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L366" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K366" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L366" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Entertainment'.</t>
         </is>
       </c>
     </row>
     <row r="367" ht="16" customHeight="1">
-      <c r="B367" s="58" t="inlineStr">
+      <c r="B367" s="71" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C367" s="58" t="inlineStr">
+      <c r="C367" s="71" t="inlineStr">
         <is>
           <t>07/17/2026</t>
         </is>
       </c>
-      <c r="D367" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E367" s="58" t="inlineStr"/>
-      <c r="F367" s="58" t="inlineStr"/>
-      <c r="G367" s="58" t="inlineStr">
+      <c r="D367" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E367" s="71" t="inlineStr"/>
+      <c r="F367" s="71" t="inlineStr"/>
+      <c r="G367" s="71" t="inlineStr">
         <is>
           <t>DD *DOORDASH ANGRYCHIC 8559731040 CA</t>
         </is>
       </c>
-      <c r="H367" s="58" t="inlineStr">
+      <c r="H367" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I367" s="59" t="n">
+      <c r="I367" s="72" t="n">
         <v>26.1</v>
       </c>
-      <c r="J367" s="59" t="n">
+      <c r="J367" s="72" t="n">
         <v>346.45</v>
       </c>
-      <c r="K367" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L367" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K367" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L367" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Entertainment'.</t>
         </is>
       </c>
     </row>
     <row r="368" ht="16" customHeight="1">
-      <c r="B368" s="58" t="inlineStr">
+      <c r="B368" s="71" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C368" s="58" t="inlineStr">
+      <c r="C368" s="71" t="inlineStr">
         <is>
           <t>07/20/2026</t>
         </is>
       </c>
-      <c r="D368" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E368" s="58" t="inlineStr"/>
-      <c r="F368" s="58" t="inlineStr"/>
-      <c r="G368" s="58" t="inlineStr">
+      <c r="D368" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E368" s="71" t="inlineStr"/>
+      <c r="F368" s="71" t="inlineStr"/>
+      <c r="G368" s="71" t="inlineStr">
         <is>
           <t>DD *DOORDASH NAGASKITC 8559731040 CA</t>
         </is>
       </c>
-      <c r="H368" s="58" t="inlineStr">
+      <c r="H368" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I368" s="59" t="n">
+      <c r="I368" s="72" t="n">
         <v>31.21</v>
       </c>
-      <c r="J368" s="59" t="n">
+      <c r="J368" s="72" t="n">
         <v>377.66</v>
       </c>
-      <c r="K368" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L368" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K368" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L368" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Entertainment'.</t>
         </is>
       </c>
     </row>
     <row r="369" ht="16" customHeight="1">
-      <c r="B369" s="58" t="inlineStr">
+      <c r="B369" s="71" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C369" s="58" t="inlineStr">
+      <c r="C369" s="71" t="inlineStr">
         <is>
           <t>07/23/2026</t>
         </is>
       </c>
-      <c r="D369" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E369" s="58" t="inlineStr"/>
-      <c r="F369" s="58" t="inlineStr"/>
-      <c r="G369" s="58" t="inlineStr">
+      <c r="D369" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E369" s="71" t="inlineStr"/>
+      <c r="F369" s="71" t="inlineStr"/>
+      <c r="G369" s="71" t="inlineStr">
         <is>
           <t>DD *DOORDASH ULAVACHAR 8559731040 CA</t>
         </is>
       </c>
-      <c r="H369" s="58" t="inlineStr">
+      <c r="H369" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I369" s="59" t="n">
+      <c r="I369" s="72" t="n">
         <v>17.98</v>
       </c>
-      <c r="J369" s="59" t="n">
+      <c r="J369" s="72" t="n">
         <v>395.64</v>
       </c>
-      <c r="K369" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L369" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K369" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L369" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Entertainment'.</t>
         </is>
       </c>
     </row>
     <row r="370" ht="16" customHeight="1">
-      <c r="B370" s="58" t="inlineStr">
+      <c r="B370" s="71" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C370" s="58" t="inlineStr">
+      <c r="C370" s="71" t="inlineStr">
         <is>
           <t>07/26/2026</t>
         </is>
       </c>
-      <c r="D370" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E370" s="58" t="inlineStr"/>
-      <c r="F370" s="58" t="inlineStr"/>
-      <c r="G370" s="58" t="inlineStr">
+      <c r="D370" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E370" s="71" t="inlineStr"/>
+      <c r="F370" s="71" t="inlineStr"/>
+      <c r="G370" s="71" t="inlineStr">
         <is>
           <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
         </is>
       </c>
-      <c r="H370" s="58" t="inlineStr">
+      <c r="H370" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I370" s="59" t="n">
+      <c r="I370" s="72" t="n">
         <v>24.94</v>
       </c>
-      <c r="J370" s="59" t="n">
+      <c r="J370" s="72" t="n">
         <v>420.58</v>
       </c>
-      <c r="K370" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L370" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K370" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L370" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Entertainment'.</t>
         </is>
       </c>
     </row>
     <row r="371" ht="16" customHeight="1">
-      <c r="B371" s="58" t="inlineStr">
+      <c r="B371" s="71" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C371" s="58" t="inlineStr">
+      <c r="C371" s="71" t="inlineStr">
         <is>
           <t>07/29/2026</t>
         </is>
       </c>
-      <c r="D371" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E371" s="58" t="inlineStr"/>
-      <c r="F371" s="58" t="inlineStr"/>
-      <c r="G371" s="58" t="inlineStr">
+      <c r="D371" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E371" s="71" t="inlineStr"/>
+      <c r="F371" s="71" t="inlineStr"/>
+      <c r="G371" s="71" t="inlineStr">
         <is>
           <t>DD *DOORDASH DECCANMOR 8559731040 CA</t>
         </is>
       </c>
-      <c r="H371" s="58" t="inlineStr">
+      <c r="H371" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I371" s="59" t="n">
+      <c r="I371" s="72" t="n">
         <v>18.5</v>
       </c>
-      <c r="J371" s="59" t="n">
+      <c r="J371" s="72" t="n">
         <v>439.08</v>
       </c>
-      <c r="K371" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L371" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K371" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L371" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Meals &amp; Entertainment:Meals with clients' based on historical data, found 'Entertainment'.</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16082,7 @@
       </c>
       <c r="L375" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16127,7 @@
       </c>
       <c r="L376" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -16792,7 +16172,7 @@
       </c>
       <c r="L377" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16262,7 @@
       </c>
       <c r="L379" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -16932,47 +16312,47 @@
       </c>
     </row>
     <row r="381" ht="16" customHeight="1">
-      <c r="B381" s="58" t="inlineStr">
+      <c r="B381" s="71" t="inlineStr">
         <is>
           <t>Meals with clients</t>
         </is>
       </c>
-      <c r="C381" s="58" t="inlineStr">
+      <c r="C381" s="71" t="inlineStr">
         <is>
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="D381" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E381" s="58" t="inlineStr"/>
-      <c r="F381" s="58" t="inlineStr"/>
-      <c r="G381" s="58" t="inlineStr">
+      <c r="D381" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E381" s="71" t="inlineStr"/>
+      <c r="F381" s="71" t="inlineStr"/>
+      <c r="G381" s="71" t="inlineStr">
         <is>
           <t>AplPay AMK BLACKROCKWILMINGTON          DE</t>
         </is>
       </c>
-      <c r="H381" s="58" t="inlineStr">
+      <c r="H381" s="71" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="I381" s="59" t="n">
+      <c r="I381" s="72" t="n">
         <v>3.59</v>
       </c>
-      <c r="J381" s="59" t="n">
+      <c r="J381" s="72" t="n">
         <v>12514.45</v>
       </c>
-      <c r="K381" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L381" s="61" t="inlineStr">
-        <is>
-          <t>Standard ledger entry</t>
+      <c r="K381" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L381" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Dues &amp; subscriptions' based on historical data, found 'Meals with clients'.</t>
         </is>
       </c>
     </row>
@@ -17197,7 +16577,7 @@
       </c>
       <c r="L386" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -17422,7 +16802,7 @@
       </c>
       <c r="L391" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+          <t>Verified: Meals &amp; Entertainment:Meals with clients</t>
         </is>
       </c>
     </row>
@@ -17697,47 +17077,47 @@
       </c>
     </row>
     <row r="398" ht="16" customHeight="1">
-      <c r="B398" s="58" t="inlineStr">
+      <c r="B398" s="71" t="inlineStr">
         <is>
           <t>Meals with clients</t>
         </is>
       </c>
-      <c r="C398" s="58" t="inlineStr">
+      <c r="C398" s="71" t="inlineStr">
         <is>
           <t>07/26/2026</t>
         </is>
       </c>
-      <c r="D398" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E398" s="58" t="inlineStr"/>
-      <c r="F398" s="58" t="inlineStr"/>
-      <c r="G398" s="58" t="inlineStr">
+      <c r="D398" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E398" s="71" t="inlineStr"/>
+      <c r="F398" s="71" t="inlineStr"/>
+      <c r="G398" s="71" t="inlineStr">
         <is>
           <t>CLUB 28 BADMINTON DELE 9176316713 DE</t>
         </is>
       </c>
-      <c r="H398" s="58" t="inlineStr">
+      <c r="H398" s="71" t="inlineStr">
         <is>
           <t>BOA CC</t>
         </is>
       </c>
-      <c r="I398" s="59" t="n">
+      <c r="I398" s="72" t="n">
         <v>140</v>
       </c>
-      <c r="J398" s="59" t="n">
+      <c r="J398" s="72" t="n">
         <v>13844.26</v>
       </c>
-      <c r="K398" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L398" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Meals &amp; Entertainment:Meals with clients</t>
+      <c r="K398" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L398" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Owners Distribution' based on historical data, found 'Meals with clients'.</t>
         </is>
       </c>
     </row>
@@ -17878,47 +17258,47 @@
       </c>
     </row>
     <row r="406" ht="16" customHeight="1">
-      <c r="B406" s="71" t="inlineStr">
+      <c r="B406" s="58" t="inlineStr">
         <is>
           <t>Office supplies</t>
         </is>
       </c>
-      <c r="C406" s="71" t="inlineStr">
+      <c r="C406" s="58" t="inlineStr">
         <is>
           <t>07/10/2026</t>
         </is>
       </c>
-      <c r="D406" s="71" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E406" s="71" t="inlineStr"/>
-      <c r="F406" s="71" t="inlineStr"/>
-      <c r="G406" s="71" t="inlineStr">
+      <c r="D406" s="58" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E406" s="58" t="inlineStr"/>
+      <c r="F406" s="58" t="inlineStr"/>
+      <c r="G406" s="58" t="inlineStr">
         <is>
           <t>PY *BANNER PEST SERVSAN JOSE            CA</t>
         </is>
       </c>
-      <c r="H406" s="71" t="inlineStr">
+      <c r="H406" s="58" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="I406" s="72" t="n">
+      <c r="I406" s="59" t="n">
         <v>150</v>
       </c>
-      <c r="J406" s="72" t="n">
+      <c r="J406" s="59" t="n">
         <v>3787.98</v>
       </c>
-      <c r="K406" s="73" t="inlineStr">
-        <is>
-          <t>CATEGORY MISMATCH</t>
-        </is>
-      </c>
-      <c r="L406" s="74" t="inlineStr">
-        <is>
-          <t>Expected 'Repairs &amp; maintenance', found 'Office supplies'.</t>
+      <c r="K406" s="60" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="L406" s="61" t="inlineStr">
+        <is>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -17963,7 +17343,7 @@
       </c>
       <c r="L407" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Office supplies</t>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -18008,7 +17388,7 @@
       </c>
       <c r="L408" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Office supplies</t>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -18053,7 +17433,7 @@
       </c>
       <c r="L409" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Office supplies</t>
+          <t>Verified: Office expenses:Office supplies</t>
         </is>
       </c>
     </row>
@@ -18154,7 +17534,7 @@
       </c>
       <c r="L416" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+          <t>Verified: Office expenses:Software &amp; apps</t>
         </is>
       </c>
     </row>
@@ -18199,52 +17579,52 @@
       </c>
       <c r="L417" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
     <row r="418" ht="16" customHeight="1">
-      <c r="B418" s="58" t="inlineStr">
+      <c r="B418" s="71" t="inlineStr">
         <is>
           <t>Software &amp; apps</t>
         </is>
       </c>
-      <c r="C418" s="58" t="inlineStr">
+      <c r="C418" s="71" t="inlineStr">
         <is>
           <t>07/16/2026</t>
         </is>
       </c>
-      <c r="D418" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E418" s="58" t="inlineStr"/>
-      <c r="F418" s="58" t="inlineStr"/>
-      <c r="G418" s="58" t="inlineStr">
+      <c r="D418" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E418" s="71" t="inlineStr"/>
+      <c r="F418" s="71" t="inlineStr"/>
+      <c r="G418" s="71" t="inlineStr">
         <is>
           <t>ANTHROPIC* CLAUDE SUSAN FRANCISCO       CA</t>
         </is>
       </c>
-      <c r="H418" s="58" t="inlineStr">
+      <c r="H418" s="71" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="I418" s="59" t="n">
+      <c r="I418" s="72" t="n">
         <v>20</v>
       </c>
-      <c r="J418" s="59" t="n">
+      <c r="J418" s="72" t="n">
         <v>2807.77</v>
       </c>
-      <c r="K418" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L418" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+      <c r="K418" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L418" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Dues &amp; subscriptions' based on historical data, found 'Software &amp; apps'.</t>
         </is>
       </c>
     </row>
@@ -18289,7 +17669,7 @@
       </c>
       <c r="L419" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Office expenses:Software &amp; apps</t>
+          <t>Verified: Office expenses:Software &amp; apps</t>
         </is>
       </c>
     </row>
@@ -18380,7 +17760,7 @@
       </c>
       <c r="L425" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -18425,7 +17805,7 @@
       </c>
       <c r="L426" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -18470,7 +17850,7 @@
       </c>
       <c r="L427" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -18515,7 +17895,7 @@
       </c>
       <c r="L428" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -18560,7 +17940,7 @@
       </c>
       <c r="L429" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Payroll expenses:Payroll Processing Fee</t>
+          <t>Verified: Payroll Processing Fee</t>
         </is>
       </c>
     </row>
@@ -18769,51 +18149,51 @@
       </c>
     </row>
     <row r="446" ht="16" customHeight="1">
-      <c r="B446" s="58" t="inlineStr">
+      <c r="B446" s="71" t="inlineStr">
         <is>
           <t>Building &amp; land rent</t>
         </is>
       </c>
-      <c r="C446" s="58" t="inlineStr">
+      <c r="C446" s="71" t="inlineStr">
         <is>
           <t>07/20/2026</t>
         </is>
       </c>
-      <c r="D446" s="58" t="inlineStr">
+      <c r="D446" s="71" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="E446" s="58" t="inlineStr"/>
-      <c r="F446" s="58" t="inlineStr">
+      <c r="E446" s="71" t="inlineStr"/>
+      <c r="F446" s="71" t="inlineStr">
         <is>
           <t>Exor Properties, LLC</t>
         </is>
       </c>
-      <c r="G446" s="58" t="inlineStr">
+      <c r="G446" s="71" t="inlineStr">
         <is>
           <t>Kindly schedule the monthly rental payment to be released on the 25th of each month</t>
         </is>
       </c>
-      <c r="H446" s="58" t="inlineStr">
+      <c r="H446" s="71" t="inlineStr">
         <is>
           <t>Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I446" s="59" t="n">
+      <c r="I446" s="72" t="n">
         <v>1650</v>
       </c>
-      <c r="J446" s="59" t="n">
+      <c r="J446" s="72" t="n">
         <v>11000</v>
       </c>
-      <c r="K446" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L446" s="61" t="inlineStr">
-        <is>
-          <t>Standard ledger entry</t>
+      <c r="K446" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L446" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Accounts Payable (A/P)' based on historical data, found 'Building &amp; land rent'.</t>
         </is>
       </c>
     </row>
@@ -19061,7 +18441,7 @@
       </c>
       <c r="L465" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
@@ -19106,7 +18486,7 @@
       </c>
       <c r="L466" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
@@ -19151,7 +18531,7 @@
       </c>
       <c r="L467" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
@@ -19196,7 +18576,7 @@
       </c>
       <c r="L468" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Auto Expenses</t>
+          <t>Verified: Travel:Auto Expenses</t>
         </is>
       </c>
     </row>
@@ -19297,7 +18677,7 @@
       </c>
       <c r="L475" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -19342,7 +18722,7 @@
       </c>
       <c r="L476" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -19387,7 +18767,7 @@
       </c>
       <c r="L477" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -19432,7 +18812,7 @@
       </c>
       <c r="L478" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -19477,7 +18857,7 @@
       </c>
       <c r="L479" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Travel:Taxis or shared rides</t>
+          <t>Verified: Travel:Taxis or shared rides</t>
         </is>
       </c>
     </row>
@@ -19614,7 +18994,7 @@
       </c>
       <c r="L490" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Electricity</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -19687,7 +19067,7 @@
       </c>
       <c r="L494" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Other</t>
+          <t>Verified: Utilities:Other</t>
         </is>
       </c>
     </row>
@@ -19760,7 +19140,7 @@
       </c>
       <c r="L498" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -19805,7 +19185,7 @@
       </c>
       <c r="L499" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -19850,7 +19230,7 @@
       </c>
       <c r="L500" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -19895,7 +19275,7 @@
       </c>
       <c r="L501" s="74" t="inlineStr">
         <is>
-          <t>Expected 'Amex CC', found 'Phone service'.</t>
+          <t>Expected 'Amex CC' based on historical data, found 'Phone service'.</t>
         </is>
       </c>
     </row>
@@ -19940,7 +19320,7 @@
       </c>
       <c r="L502" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Utilities:Phone service</t>
+          <t>Verified: Utilities:Phone service</t>
         </is>
       </c>
     </row>
@@ -20087,52 +19467,52 @@
       </c>
       <c r="L510" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Gas And Fuel</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
     <row r="511" ht="16" customHeight="1">
-      <c r="B511" s="58" t="inlineStr">
+      <c r="B511" s="71" t="inlineStr">
         <is>
           <t>Gas And Fuel</t>
         </is>
       </c>
-      <c r="C511" s="58" t="inlineStr">
+      <c r="C511" s="71" t="inlineStr">
         <is>
           <t>07/18/2026</t>
         </is>
       </c>
-      <c r="D511" s="58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E511" s="58" t="inlineStr"/>
-      <c r="F511" s="58" t="inlineStr"/>
-      <c r="G511" s="58" t="inlineStr">
+      <c r="D511" s="71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E511" s="71" t="inlineStr"/>
+      <c r="F511" s="71" t="inlineStr"/>
+      <c r="G511" s="71" t="inlineStr">
         <is>
           <t>UNION 76 09439498   FREMONT             CA</t>
         </is>
       </c>
-      <c r="H511" s="58" t="inlineStr">
+      <c r="H511" s="71" t="inlineStr">
         <is>
           <t>Amex CC</t>
         </is>
       </c>
-      <c r="I511" s="59" t="n">
+      <c r="I511" s="72" t="n">
         <v>105.17</v>
       </c>
-      <c r="J511" s="59" t="n">
+      <c r="J511" s="72" t="n">
         <v>1089.11</v>
       </c>
-      <c r="K511" s="60" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="L511" s="61" t="inlineStr">
-        <is>
-          <t>Matched to historical category: Gas And Fuel</t>
+      <c r="K511" s="73" t="inlineStr">
+        <is>
+          <t>CATEGORY MISMATCH</t>
+        </is>
+      </c>
+      <c r="L511" s="74" t="inlineStr">
+        <is>
+          <t>Expected 'Travel:Auto Expenses' based on historical data, found 'Gas And Fuel'.</t>
         </is>
       </c>
     </row>
@@ -20177,7 +19557,7 @@
       </c>
       <c r="L512" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Gas And Fuel</t>
+          <t>Verified: Gas And Fuel</t>
         </is>
       </c>
     </row>
@@ -20257,7 +19637,7 @@
       </c>
       <c r="L517" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Vehicle expenses:Parking &amp; tolls</t>
+          <t>Verified: Vehicle expenses:Parking &amp; tolls</t>
         </is>
       </c>
     </row>
@@ -20302,7 +19682,7 @@
       </c>
       <c r="L518" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Vehicle expenses:Parking &amp; tolls</t>
+          <t>Standard ledger entry</t>
         </is>
       </c>
     </row>
@@ -20347,7 +19727,7 @@
       </c>
       <c r="L519" s="61" t="inlineStr">
         <is>
-          <t>Matched to historical category: Vehicle expenses:Parking &amp; tolls</t>
+          <t>Verified: Vehicle expenses:Parking &amp; tolls</t>
         </is>
       </c>
     </row>
